--- a/2026_project/2_data_processed/intermediate_output/combined_selected_manual_edit.xlsx
+++ b/2026_project/2_data_processed/intermediate_output/combined_selected_manual_edit.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dutka\MT\AdOpT-NET0_dw\2026_project\2_data_processed\intermediate_output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C22CB761-4EF8-4EF1-8ACC-FBF4D072F563}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61AA55CF-9FDD-4A1F-9AD6-38243B7C764A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-1180" yWindow="0" windowWidth="23040" windowHeight="13200" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="10000" yWindow="2110" windowWidth="12220" windowHeight="7510" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1041,6 +1041,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:P145"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -1098,7 +1099,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B2" t="s">
         <v>15</v>
       </c>
@@ -1139,7 +1140,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
         <v>21</v>
       </c>
@@ -1180,7 +1181,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
         <v>22</v>
       </c>
@@ -1221,7 +1222,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
         <v>26</v>
       </c>
@@ -1262,7 +1263,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B6" t="s">
         <v>28</v>
       </c>
@@ -1303,7 +1304,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B7" t="s">
         <v>30</v>
       </c>
@@ -1344,7 +1345,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="8" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B8" t="s">
         <v>32</v>
       </c>
@@ -1385,7 +1386,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="9" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B9" t="s">
         <v>33</v>
       </c>
@@ -1426,7 +1427,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="10" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B10" t="s">
         <v>35</v>
       </c>
@@ -1467,7 +1468,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="11" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B11" t="s">
         <v>37</v>
       </c>
@@ -1508,7 +1509,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="12" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B12" t="s">
         <v>39</v>
       </c>
@@ -1549,7 +1550,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B13" t="s">
         <v>42</v>
       </c>
@@ -1590,7 +1591,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B14" t="s">
         <v>43</v>
       </c>
@@ -1631,7 +1632,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="15" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B15" t="s">
         <v>44</v>
       </c>
@@ -1672,7 +1673,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="16" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B16" t="s">
         <v>45</v>
       </c>
@@ -1713,7 +1714,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="17" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="17" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B17" t="s">
         <v>46</v>
       </c>
@@ -1754,7 +1755,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="18" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="18" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B18" t="s">
         <v>47</v>
       </c>
@@ -1795,7 +1796,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="19" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="19" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B19" t="s">
         <v>49</v>
       </c>
@@ -1836,7 +1837,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="20" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="20" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B20" t="s">
         <v>50</v>
       </c>
@@ -1877,7 +1878,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="21" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="21" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B21" t="s">
         <v>51</v>
       </c>
@@ -1918,7 +1919,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="22" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="22" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B22" t="s">
         <v>52</v>
       </c>
@@ -1959,7 +1960,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="23" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B23" t="s">
         <v>53</v>
       </c>
@@ -2000,7 +2001,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="24" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="24" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B24" t="s">
         <v>55</v>
       </c>
@@ -2041,7 +2042,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="25" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="25" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B25" t="s">
         <v>56</v>
       </c>
@@ -2082,7 +2083,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="26" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="26" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B26" t="s">
         <v>57</v>
       </c>
@@ -2123,7 +2124,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="27" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="27" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B27" t="s">
         <v>58</v>
       </c>
@@ -2164,7 +2165,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="28" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="28" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B28" t="s">
         <v>60</v>
       </c>
@@ -2205,7 +2206,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="29" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="29" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B29" t="s">
         <v>61</v>
       </c>
@@ -2246,7 +2247,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="30" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="30" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B30" t="s">
         <v>62</v>
       </c>
@@ -2287,7 +2288,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="31" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="31" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B31" t="s">
         <v>63</v>
       </c>
@@ -2328,7 +2329,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="32" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="32" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B32" t="s">
         <v>64</v>
       </c>
@@ -2369,7 +2370,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="33" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="33" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B33" t="s">
         <v>65</v>
       </c>
@@ -2410,7 +2411,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="34" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="34" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B34" t="s">
         <v>66</v>
       </c>
@@ -2451,7 +2452,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="35" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="35" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B35" t="s">
         <v>68</v>
       </c>
@@ -2492,7 +2493,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="36" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="36" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B36" t="s">
         <v>69</v>
       </c>
@@ -2533,7 +2534,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="37" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="37" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B37" t="s">
         <v>70</v>
       </c>
@@ -2574,7 +2575,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="38" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="38" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B38" t="s">
         <v>72</v>
       </c>
@@ -2615,7 +2616,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="39" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="39" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B39" t="s">
         <v>73</v>
       </c>
@@ -2656,7 +2657,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="40" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="40" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B40" t="s">
         <v>74</v>
       </c>
@@ -2697,7 +2698,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="41" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="41" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B41" t="s">
         <v>75</v>
       </c>
@@ -2738,7 +2739,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="42" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="42" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B42" t="s">
         <v>76</v>
       </c>
@@ -2779,7 +2780,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="43" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="43" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B43" t="s">
         <v>77</v>
       </c>
@@ -2820,7 +2821,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="44" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="44" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B44" t="s">
         <v>78</v>
       </c>
@@ -2861,7 +2862,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="45" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B45" t="s">
         <v>79</v>
       </c>
@@ -2902,7 +2903,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="46" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="46" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B46" t="s">
         <v>81</v>
       </c>
@@ -2943,7 +2944,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="47" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="47" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B47" t="s">
         <v>82</v>
       </c>
@@ -2984,7 +2985,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="48" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="48" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B48" t="s">
         <v>84</v>
       </c>
@@ -3025,7 +3026,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="49" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="49" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B49" t="s">
         <v>85</v>
       </c>
@@ -3066,7 +3067,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="50" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="50" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B50" t="s">
         <v>86</v>
       </c>
@@ -3107,7 +3108,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="51" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="51" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B51" t="s">
         <v>87</v>
       </c>
@@ -3148,7 +3149,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="52" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="52" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B52" t="s">
         <v>88</v>
       </c>
@@ -3189,7 +3190,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="53" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="53" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B53" t="s">
         <v>89</v>
       </c>
@@ -3230,7 +3231,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="54" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="54" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B54" t="s">
         <v>91</v>
       </c>
@@ -3271,7 +3272,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="55" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="55" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B55" t="s">
         <v>92</v>
       </c>
@@ -3312,7 +3313,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="56" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="56" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B56" t="s">
         <v>93</v>
       </c>
@@ -3353,7 +3354,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="57" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="57" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B57" t="s">
         <v>94</v>
       </c>
@@ -3394,7 +3395,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="58" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="58" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B58" t="s">
         <v>95</v>
       </c>
@@ -3435,7 +3436,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="59" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="59" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B59" t="s">
         <v>96</v>
       </c>
@@ -3476,7 +3477,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="60" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="60" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B60" t="s">
         <v>97</v>
       </c>
@@ -3517,7 +3518,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="61" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="61" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B61" t="s">
         <v>98</v>
       </c>
@@ -3558,7 +3559,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="62" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="62" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B62" t="s">
         <v>99</v>
       </c>
@@ -3599,7 +3600,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="63" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="63" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B63" t="s">
         <v>100</v>
       </c>
@@ -3640,7 +3641,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="64" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="64" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B64" t="s">
         <v>101</v>
       </c>
@@ -3681,7 +3682,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="65" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="65" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B65" t="s">
         <v>102</v>
       </c>
@@ -3722,7 +3723,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="66" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="66" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B66" t="s">
         <v>103</v>
       </c>
@@ -3763,7 +3764,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="67" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="67" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B67" t="s">
         <v>105</v>
       </c>
@@ -3804,7 +3805,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="68" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="68" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B68" t="s">
         <v>106</v>
       </c>
@@ -3845,7 +3846,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="69" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="69" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B69" t="s">
         <v>108</v>
       </c>
@@ -3886,7 +3887,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="70" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="70" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B70" t="s">
         <v>109</v>
       </c>
@@ -3927,7 +3928,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="71" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="71" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B71" t="s">
         <v>110</v>
       </c>
@@ -3968,7 +3969,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="72" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="72" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B72" t="s">
         <v>111</v>
       </c>
@@ -4009,7 +4010,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="73" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="73" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B73" t="s">
         <v>112</v>
       </c>
@@ -4050,7 +4051,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="74" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="74" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B74" t="s">
         <v>114</v>
       </c>
@@ -4091,7 +4092,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="75" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="75" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B75" t="s">
         <v>115</v>
       </c>
@@ -4132,7 +4133,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="76" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="76" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B76" t="s">
         <v>116</v>
       </c>
@@ -4173,7 +4174,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="77" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B77" t="s">
         <v>117</v>
       </c>
@@ -4214,7 +4215,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="78" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="78" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B78" t="s">
         <v>118</v>
       </c>
@@ -4255,7 +4256,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="79" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B79" t="s">
         <v>119</v>
       </c>
@@ -4296,7 +4297,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="80" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="80" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B80" t="s">
         <v>120</v>
       </c>
@@ -4337,7 +4338,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="81" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B81" t="s">
         <v>122</v>
       </c>
@@ -4378,7 +4379,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="82" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B82" t="s">
         <v>123</v>
       </c>
@@ -4419,7 +4420,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="83" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B83" t="s">
         <v>124</v>
       </c>
@@ -4460,7 +4461,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="84" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B84" t="s">
         <v>125</v>
       </c>
@@ -4501,7 +4502,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="85" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B85" t="s">
         <v>127</v>
       </c>
@@ -4542,7 +4543,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="86" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B86" t="s">
         <v>129</v>
       </c>
@@ -4583,7 +4584,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="87" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B87" t="s">
         <v>130</v>
       </c>
@@ -4624,7 +4625,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="88" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B88" t="s">
         <v>131</v>
       </c>
@@ -4665,7 +4666,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="89" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B89" t="s">
         <v>132</v>
       </c>
@@ -4706,7 +4707,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="90" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
         <v>133</v>
       </c>
@@ -4741,7 +4742,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="91" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
         <v>137</v>
       </c>
@@ -4776,7 +4777,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="92" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
         <v>139</v>
       </c>
@@ -4811,7 +4812,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="93" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
         <v>142</v>
       </c>
@@ -4846,7 +4847,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="94" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
         <v>145</v>
       </c>
@@ -4881,7 +4882,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="95" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
         <v>148</v>
       </c>
@@ -4916,7 +4917,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="96" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
         <v>150</v>
       </c>
@@ -4951,7 +4952,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="97" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="97" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B97" t="s">
         <v>153</v>
       </c>
@@ -4980,7 +4981,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="98" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="98" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B98" t="s">
         <v>156</v>
       </c>
@@ -5009,7 +5010,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="99" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="99" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B99" t="s">
         <v>157</v>
       </c>
@@ -5038,7 +5039,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="100" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="100" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B100" t="s">
         <v>158</v>
       </c>
@@ -5067,7 +5068,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="101" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="101" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B101" t="s">
         <v>159</v>
       </c>
@@ -5096,7 +5097,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="102" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="102" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B102" t="s">
         <v>160</v>
       </c>
@@ -5125,7 +5126,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="103" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="103" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B103" t="s">
         <v>161</v>
       </c>
@@ -5154,7 +5155,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="104" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="104" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B104" t="s">
         <v>163</v>
       </c>
@@ -5183,7 +5184,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="105" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="105" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B105" t="s">
         <v>164</v>
       </c>
@@ -5212,7 +5213,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="106" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="106" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B106" t="s">
         <v>166</v>
       </c>
@@ -5241,7 +5242,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="107" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="107" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B107" t="s">
         <v>167</v>
       </c>
@@ -5270,7 +5271,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="108" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="108" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B108" t="s">
         <v>74</v>
       </c>
@@ -5299,7 +5300,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="109" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="109" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B109" t="s">
         <v>168</v>
       </c>
@@ -5328,7 +5329,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="110" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="110" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B110" t="s">
         <v>169</v>
       </c>
@@ -5357,7 +5358,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="111" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="111" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B111" t="s">
         <v>79</v>
       </c>
@@ -5386,7 +5387,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="112" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="112" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B112" t="s">
         <v>93</v>
       </c>
@@ -5415,7 +5416,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="113" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="113" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B113" t="s">
         <v>170</v>
       </c>
@@ -5444,7 +5445,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="114" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="114" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B114" t="s">
         <v>171</v>
       </c>
@@ -5473,7 +5474,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="115" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="115" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B115" t="s">
         <v>172</v>
       </c>
@@ -5502,7 +5503,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="116" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="116" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B116" t="s">
         <v>173</v>
       </c>
@@ -5531,7 +5532,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="117" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="117" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B117" t="s">
         <v>174</v>
       </c>
@@ -5560,7 +5561,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="118" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="118" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B118" t="s">
         <v>175</v>
       </c>
@@ -5589,7 +5590,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="119" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="119" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B119" t="s">
         <v>176</v>
       </c>
@@ -5618,7 +5619,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="120" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="120" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B120" t="s">
         <v>177</v>
       </c>
@@ -5647,7 +5648,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="121" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="121" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B121" t="s">
         <v>178</v>
       </c>
@@ -5676,7 +5677,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="122" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="122" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B122" t="s">
         <v>179</v>
       </c>
@@ -5705,7 +5706,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="123" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="123" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B123" t="s">
         <v>180</v>
       </c>
@@ -5734,7 +5735,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="124" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="124" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B124" t="s">
         <v>181</v>
       </c>
@@ -5763,7 +5764,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="125" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="125" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B125" t="s">
         <v>182</v>
       </c>
@@ -5792,7 +5793,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="126" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="126" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B126" t="s">
         <v>183</v>
       </c>
@@ -5821,7 +5822,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="127" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="127" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B127" t="s">
         <v>184</v>
       </c>
@@ -5850,7 +5851,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="128" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="128" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B128" t="s">
         <v>185</v>
       </c>
@@ -5879,7 +5880,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="129" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="129" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B129" t="s">
         <v>186</v>
       </c>
@@ -5908,7 +5909,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="130" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="130" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B130" t="s">
         <v>187</v>
       </c>
@@ -5937,7 +5938,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="131" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="131" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B131" t="s">
         <v>188</v>
       </c>
@@ -5966,7 +5967,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="132" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="132" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B132" t="s">
         <v>189</v>
       </c>
@@ -5995,7 +5996,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="133" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="133" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B133" t="s">
         <v>190</v>
       </c>
@@ -6024,7 +6025,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="134" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="134" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B134" t="s">
         <v>191</v>
       </c>
@@ -6050,7 +6051,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="135" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="135" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B135" t="s">
         <v>192</v>
       </c>
@@ -6079,7 +6080,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="136" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="136" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B136" t="s">
         <v>193</v>
       </c>
@@ -6108,7 +6109,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="137" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="137" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B137" t="s">
         <v>117</v>
       </c>
@@ -6137,7 +6138,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="138" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="138" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B138" t="s">
         <v>194</v>
       </c>
@@ -6192,10 +6193,10 @@
         <v>20</v>
       </c>
       <c r="P139" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="140" spans="2:16" x14ac:dyDescent="0.35">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="140" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B140" t="s">
         <v>127</v>
       </c>
@@ -6224,7 +6225,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="141" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="141" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B141" t="s">
         <v>196</v>
       </c>
@@ -6253,7 +6254,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="142" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="142" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B142" t="s">
         <v>99</v>
       </c>
@@ -6282,7 +6283,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="143" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="143" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B143" t="s">
         <v>33</v>
       </c>
@@ -6311,7 +6312,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="144" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="144" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B144" t="s">
         <v>197</v>
       </c>
@@ -6340,7 +6341,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="145" spans="2:16" x14ac:dyDescent="0.35">
+    <row r="145" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B145" t="s">
         <v>198</v>
       </c>
@@ -6370,7 +6371,18 @@
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P145" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A1:P145" xr:uid="{00000000-0001-0000-0000-000000000000}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="Trieste"/>
+      </filters>
+    </filterColumn>
+    <filterColumn colId="15">
+      <filters>
+        <filter val="Yes"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
   <conditionalFormatting sqref="P1:P1048576">
     <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="Yes">
       <formula>NOT(ISERROR(SEARCH("Yes",P1)))</formula>

--- a/2026_project/2_data_processed/intermediate_output/combined_selected_manual_edit.xlsx
+++ b/2026_project/2_data_processed/intermediate_output/combined_selected_manual_edit.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dutka\MT\AdOpT-NET0_dw\2026_project\2_data_processed\intermediate_output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{61AA55CF-9FDD-4A1F-9AD6-38243B7C764A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{215FC4D1-FB24-4F0F-A277-58BDE8E06228}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10000" yWindow="2110" windowWidth="12220" windowHeight="7510" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-270" yWindow="2080" windowWidth="25470" windowHeight="9220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -18,20 +18,7 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$P$145</definedName>
   </definedNames>
-  <calcPr calcId="191029"/>
-  <extLst>
-    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
-      <xcalcf:calcFeatures>
-        <xcalcf:feature name="microsoft.com:RD"/>
-        <xcalcf:feature name="microsoft.com:Single"/>
-        <xcalcf:feature name="microsoft.com:FV"/>
-        <xcalcf:feature name="microsoft.com:CNMTM"/>
-        <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
-      </xcalcf:calcFeatures>
-    </ext>
-  </extLst>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
@@ -83,6 +70,9 @@
     <t>xiao_emitters</t>
   </si>
   <si>
+    <t>selection</t>
+  </si>
+  <si>
     <t>ACCIAI SPECIALI TERNI S.P.A. - stabilimento di TERNI</t>
   </si>
   <si>
@@ -101,6 +91,9 @@
     <t>No</t>
   </si>
   <si>
+    <t>Yes</t>
+  </si>
+  <si>
     <t>ACCIAIERIE BERTOLI SAFAU SPA</t>
   </si>
   <si>
@@ -161,9 +154,6 @@
     <t>BUZZI UNICEM S.p.A</t>
   </si>
   <si>
-    <t>Yes</t>
-  </si>
-  <si>
     <t>BUZZI UNICEM SPA</t>
   </si>
   <si>
@@ -633,9 +623,6 @@
   </si>
   <si>
     <t>Revithoussa LNG Terminal</t>
-  </si>
-  <si>
-    <t>selection</t>
   </si>
 </sst>
 </file>
@@ -654,24 +641,17 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
-      <family val="2"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -694,56 +674,20 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
-  <dxfs count="2">
-    <dxf>
-      <font>
-        <color rgb="FF9C0006"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFFFC7CE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <color rgb="FF006100"/>
-      </font>
-      <fill>
-        <patternFill>
-          <bgColor rgb="FFC6EFCE"/>
-        </patternFill>
-      </fill>
-    </dxf>
-  </dxfs>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
@@ -1045,8 +989,12 @@
   <dimension ref="A1:P145"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="2" max="2" width="19.1796875" customWidth="1"/>
-    <col min="16" max="16" width="8.7265625" style="3"/>
+    <col min="4" max="4" width="11.81640625" customWidth="1"/>
+    <col min="5" max="5" width="21.36328125" customWidth="1"/>
+    <col min="13" max="13" width="24.90625" customWidth="1"/>
+    <col min="14" max="14" width="22" customWidth="1"/>
+    <col min="15" max="15" width="16.453125" customWidth="1"/>
+    <col min="16" max="16" width="26.6328125" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.35">
@@ -1095,16 +1043,16 @@
       <c r="O1" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="P1" s="2" t="s">
-        <v>199</v>
+      <c r="P1" s="1" t="s">
+        <v>15</v>
       </c>
     </row>
     <row r="2" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="C2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D2">
         <v>42.566699999999997</v>
@@ -1116,36 +1064,36 @@
         <v>305433.09999999998</v>
       </c>
       <c r="H2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J2" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L2">
         <v>2023</v>
       </c>
       <c r="M2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="N2">
         <v>34.866792237442922</v>
       </c>
       <c r="O2" t="s">
-        <v>20</v>
-      </c>
-      <c r="P2" s="3" t="s">
-        <v>41</v>
+        <v>21</v>
+      </c>
+      <c r="P2" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="C3" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D3">
         <v>46.006700000000002</v>
@@ -1157,36 +1105,36 @@
         <v>259007</v>
       </c>
       <c r="H3" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I3" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J3" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L3">
         <v>2023</v>
       </c>
       <c r="M3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="N3">
         <v>29.56700913242009</v>
       </c>
       <c r="O3" t="s">
-        <v>20</v>
-      </c>
-      <c r="P3" s="3" t="s">
-        <v>41</v>
+        <v>21</v>
+      </c>
+      <c r="P3" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="4" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="C4" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D4">
         <v>32.423500557796601</v>
@@ -1198,36 +1146,36 @@
         <v>967827.94824338704</v>
       </c>
       <c r="H4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J4" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L4">
         <v>2025</v>
       </c>
       <c r="M4" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="N4">
         <v>110.4826424935373</v>
       </c>
       <c r="O4" t="s">
-        <v>20</v>
-      </c>
-      <c r="P4" s="3" t="s">
-        <v>41</v>
+        <v>21</v>
+      </c>
+      <c r="P4" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="C5" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D5">
         <v>43.465510000000002</v>
@@ -1239,36 +1187,36 @@
         <v>3732999.9360000002</v>
       </c>
       <c r="H5" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J5" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L5">
         <v>2024</v>
       </c>
       <c r="M5" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="N5">
         <v>426.14154520547947</v>
       </c>
       <c r="O5" t="s">
-        <v>20</v>
-      </c>
-      <c r="P5" s="3" t="s">
-        <v>41</v>
+        <v>21</v>
+      </c>
+      <c r="P5" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B6" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C6" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D6">
         <v>45.1494</v>
@@ -1280,36 +1228,36 @@
         <v>378667</v>
       </c>
       <c r="H6" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I6" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J6" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L6">
         <v>2023</v>
       </c>
       <c r="M6" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="N6">
         <v>43.226826484018268</v>
       </c>
       <c r="O6" t="s">
-        <v>20</v>
-      </c>
-      <c r="P6" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="P6" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="7" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B7" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C7" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D7">
         <v>36.868661270599297</v>
@@ -1321,36 +1269,36 @@
         <v>984166.4892579451</v>
       </c>
       <c r="H7" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I7" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L7">
         <v>2025</v>
       </c>
       <c r="M7" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="N7">
         <v>112.34777274634079</v>
       </c>
       <c r="O7" t="s">
-        <v>20</v>
-      </c>
-      <c r="P7" s="3" t="s">
-        <v>41</v>
+        <v>21</v>
+      </c>
+      <c r="P7" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C8" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D8">
         <v>32.520679750585899</v>
@@ -1362,36 +1310,36 @@
         <v>474779.82716398779</v>
       </c>
       <c r="H8" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I8" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J8" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L8">
         <v>2025</v>
       </c>
       <c r="M8" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="N8">
         <v>54.198610406847919</v>
       </c>
       <c r="O8" t="s">
-        <v>20</v>
-      </c>
-      <c r="P8" s="3" t="s">
-        <v>41</v>
+        <v>21</v>
+      </c>
+      <c r="P8" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="9" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B9" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C9" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D9">
         <v>34.335107767925798</v>
@@ -1403,36 +1351,36 @@
         <v>1508547.8450828581</v>
       </c>
       <c r="H9" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I9" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J9" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L9">
         <v>2025</v>
       </c>
       <c r="M9" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="N9">
         <v>172.20865811448149</v>
       </c>
       <c r="O9" t="s">
-        <v>20</v>
-      </c>
-      <c r="P9" s="3" t="s">
-        <v>41</v>
+        <v>21</v>
+      </c>
+      <c r="P9" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="10" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B10" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C10" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D10">
         <v>31.119723669408199</v>
@@ -1444,36 +1392,36 @@
         <v>1493091.3958554219</v>
       </c>
       <c r="H10" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I10" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J10" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L10">
         <v>2025</v>
       </c>
       <c r="M10" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="N10">
         <v>170.44422327116689</v>
       </c>
       <c r="O10" t="s">
-        <v>20</v>
-      </c>
-      <c r="P10" s="3" t="s">
-        <v>41</v>
+        <v>21</v>
+      </c>
+      <c r="P10" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="11" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B11" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C11" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D11">
         <v>46.068649999999998</v>
@@ -1485,36 +1433,36 @@
         <v>684374</v>
       </c>
       <c r="H11" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I11" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J11" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L11">
         <v>2024</v>
       </c>
       <c r="M11" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="N11">
         <v>78.12488584474886</v>
       </c>
       <c r="O11" t="s">
-        <v>20</v>
-      </c>
-      <c r="P11" s="3" t="s">
-        <v>41</v>
+        <v>21</v>
+      </c>
+      <c r="P11" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="12" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B12" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C12" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D12">
         <v>44.7667</v>
@@ -1526,36 +1474,36 @@
         <v>488155.33600000001</v>
       </c>
       <c r="H12" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I12" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J12" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L12">
         <v>2023</v>
       </c>
       <c r="M12" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="N12">
         <v>55.72549497716895</v>
       </c>
       <c r="O12" t="s">
-        <v>41</v>
-      </c>
-      <c r="P12" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
+      </c>
+      <c r="P12" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="13" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B13" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="C13" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D13">
         <v>44.283299999999997</v>
@@ -1567,36 +1515,36 @@
         <v>700973.36</v>
       </c>
       <c r="H13" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I13" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J13" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L13">
         <v>2023</v>
       </c>
       <c r="M13" t="s">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="N13">
         <v>80.019789954337895</v>
       </c>
       <c r="O13" t="s">
-        <v>41</v>
-      </c>
-      <c r="P13" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
+      </c>
+      <c r="P13" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="14" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B14" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="C14" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D14">
         <v>45.254199999999997</v>
@@ -1608,36 +1556,36 @@
         <v>349657.24900000001</v>
       </c>
       <c r="H14" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I14" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J14" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L14">
         <v>2023</v>
       </c>
       <c r="M14" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="N14">
         <v>39.915211073059361</v>
       </c>
       <c r="O14" t="s">
-        <v>41</v>
-      </c>
-      <c r="P14" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
+      </c>
+      <c r="P14" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="15" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B15" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="C15" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D15">
         <v>38.4563347262105</v>
@@ -1649,36 +1597,36 @@
         <v>493234.8586345205</v>
       </c>
       <c r="H15" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I15" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J15" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L15">
         <v>2025</v>
       </c>
       <c r="M15" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="N15">
         <v>56.305349159191827</v>
       </c>
       <c r="O15" t="s">
-        <v>20</v>
-      </c>
-      <c r="P15" s="3" t="s">
-        <v>41</v>
+        <v>21</v>
+      </c>
+      <c r="P15" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="16" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B16" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="C16" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D16">
         <v>32.005901759509598</v>
@@ -1690,36 +1638,36 @@
         <v>654454.01281724276</v>
       </c>
       <c r="H16" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I16" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J16" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L16">
         <v>2025</v>
       </c>
       <c r="M16" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
       <c r="N16">
         <v>74.709362193749172</v>
       </c>
       <c r="O16" t="s">
-        <v>20</v>
-      </c>
-      <c r="P16" s="3" t="s">
-        <v>41</v>
+        <v>21</v>
+      </c>
+      <c r="P16" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="17" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B17" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="C17" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D17">
         <v>30.880353032662399</v>
@@ -1731,36 +1679,36 @@
         <v>2366107.1811744389</v>
       </c>
       <c r="H17" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I17" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J17" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L17">
         <v>2025</v>
       </c>
       <c r="M17" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="N17">
         <v>270.10355949479901</v>
       </c>
       <c r="O17" t="s">
-        <v>20</v>
-      </c>
-      <c r="P17" s="3" t="s">
-        <v>41</v>
+        <v>21</v>
+      </c>
+      <c r="P17" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="18" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B18" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="C18" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D18">
         <v>41.5488546799657</v>
@@ -1772,36 +1720,36 @@
         <v>520149.38131691993</v>
       </c>
       <c r="H18" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I18" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J18" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L18">
         <v>2025</v>
       </c>
       <c r="M18" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="N18">
         <v>59.37778325535615</v>
       </c>
       <c r="O18" t="s">
-        <v>20</v>
-      </c>
-      <c r="P18" s="3" t="s">
-        <v>41</v>
+        <v>21</v>
+      </c>
+      <c r="P18" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="19" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B19" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C19" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D19">
         <v>37.194443999999997</v>
@@ -1813,36 +1761,36 @@
         <v>395619.44099999999</v>
       </c>
       <c r="H19" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I19" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J19" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L19">
         <v>2023</v>
       </c>
       <c r="M19" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="N19">
         <v>45.162036643835613</v>
       </c>
       <c r="O19" t="s">
-        <v>20</v>
-      </c>
-      <c r="P19" s="3" t="s">
-        <v>41</v>
+        <v>21</v>
+      </c>
+      <c r="P19" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="20" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B20" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C20" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D20">
         <v>41.316699999999997</v>
@@ -1854,36 +1802,36 @@
         <v>326744.86</v>
       </c>
       <c r="H20" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I20" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J20" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L20">
         <v>2023</v>
       </c>
       <c r="M20" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="N20">
         <v>37.299641552511417</v>
       </c>
       <c r="O20" t="s">
-        <v>20</v>
-      </c>
-      <c r="P20" s="3" t="s">
-        <v>41</v>
+        <v>21</v>
+      </c>
+      <c r="P20" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="21" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B21" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C21" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D21">
         <v>42.000100000000003</v>
@@ -1895,36 +1843,36 @@
         <v>383770.34899999999</v>
       </c>
       <c r="H21" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I21" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J21" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L21">
         <v>2023</v>
       </c>
       <c r="M21" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="N21">
         <v>43.809400570776248</v>
       </c>
       <c r="O21" t="s">
-        <v>20</v>
-      </c>
-      <c r="P21" s="3" t="s">
-        <v>41</v>
+        <v>21</v>
+      </c>
+      <c r="P21" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="22" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B22" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C22" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D22">
         <v>45.877777000000002</v>
@@ -1936,36 +1884,36 @@
         <v>332973</v>
       </c>
       <c r="H22" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I22" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J22" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L22">
         <v>2023</v>
       </c>
       <c r="M22" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="N22">
         <v>38.010616438356173</v>
       </c>
       <c r="O22" t="s">
-        <v>41</v>
-      </c>
-      <c r="P22" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
+      </c>
+      <c r="P22" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="23" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B23" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C23" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D23">
         <v>41.408723000000002</v>
@@ -1977,36 +1925,36 @@
         <v>905000</v>
       </c>
       <c r="H23" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I23" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J23" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L23">
         <v>2024</v>
       </c>
       <c r="M23" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="N23">
         <v>103.310502283105</v>
       </c>
       <c r="O23" t="s">
-        <v>20</v>
-      </c>
-      <c r="P23" s="3" t="s">
-        <v>41</v>
+        <v>21</v>
+      </c>
+      <c r="P23" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="24" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B24" t="s">
+        <v>56</v>
+      </c>
+      <c r="C24" t="s">
         <v>55</v>
-      </c>
-      <c r="C24" t="s">
-        <v>54</v>
       </c>
       <c r="D24">
         <v>41.314664999999998</v>
@@ -2018,36 +1966,36 @@
         <v>928000</v>
       </c>
       <c r="H24" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I24" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J24" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L24">
         <v>2024</v>
       </c>
       <c r="M24" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="N24">
         <v>105.93607305936069</v>
       </c>
       <c r="O24" t="s">
-        <v>20</v>
-      </c>
-      <c r="P24" s="3" t="s">
-        <v>41</v>
+        <v>21</v>
+      </c>
+      <c r="P24" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="25" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B25" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C25" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D25">
         <v>40.578910999999998</v>
@@ -2059,36 +2007,36 @@
         <v>592000</v>
       </c>
       <c r="H25" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I25" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J25" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L25">
         <v>2024</v>
       </c>
       <c r="M25" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="N25">
         <v>67.579908675799089</v>
       </c>
       <c r="O25" t="s">
-        <v>20</v>
-      </c>
-      <c r="P25" s="3" t="s">
-        <v>41</v>
+        <v>21</v>
+      </c>
+      <c r="P25" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="26" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B26" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C26" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D26">
         <v>38.378608</v>
@@ -2100,36 +2048,36 @@
         <v>584000</v>
       </c>
       <c r="H26" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I26" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J26" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L26">
         <v>2024</v>
       </c>
       <c r="M26" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="N26">
         <v>66.666666666666671</v>
       </c>
       <c r="O26" t="s">
-        <v>20</v>
-      </c>
-      <c r="P26" s="3" t="s">
-        <v>41</v>
+        <v>21</v>
+      </c>
+      <c r="P26" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="27" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B27" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="C27" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D27">
         <v>41.445599999999999</v>
@@ -2141,36 +2089,36 @@
         <v>689345</v>
       </c>
       <c r="H27" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I27" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J27" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L27">
         <v>2023</v>
       </c>
       <c r="M27" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="N27">
         <v>78.692351598173516</v>
       </c>
       <c r="O27" t="s">
-        <v>20</v>
-      </c>
-      <c r="P27" s="3" t="s">
-        <v>41</v>
+        <v>21</v>
+      </c>
+      <c r="P27" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="28" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B28" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="C28" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D28">
         <v>43.284399999999998</v>
@@ -2182,36 +2130,36 @@
         <v>336074</v>
       </c>
       <c r="H28" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I28" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J28" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L28">
         <v>2023</v>
       </c>
       <c r="M28" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="N28">
         <v>38.364611872146121</v>
       </c>
       <c r="O28" t="s">
-        <v>20</v>
-      </c>
-      <c r="P28" s="3" t="s">
-        <v>41</v>
+        <v>21</v>
+      </c>
+      <c r="P28" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="29" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="C29" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D29">
         <v>43.658099999999997</v>
@@ -2223,36 +2171,36 @@
         <v>402310</v>
       </c>
       <c r="H29" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I29" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J29" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L29">
         <v>2023</v>
       </c>
       <c r="M29" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="N29">
         <v>45.925799086757991</v>
       </c>
       <c r="O29" t="s">
-        <v>20</v>
-      </c>
-      <c r="P29" s="3" t="s">
-        <v>41</v>
+        <v>21</v>
+      </c>
+      <c r="P29" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="30" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B30" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="C30" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D30">
         <v>40.9497</v>
@@ -2264,36 +2212,36 @@
         <v>246153.96</v>
       </c>
       <c r="H30" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I30" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J30" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L30">
         <v>2023</v>
       </c>
       <c r="M30" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="N30">
         <v>28.09976712328767</v>
       </c>
       <c r="O30" t="s">
-        <v>20</v>
-      </c>
-      <c r="P30" s="3" t="s">
-        <v>41</v>
+        <v>21</v>
+      </c>
+      <c r="P30" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="31" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B31" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="C31" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D31">
         <v>46.177799999999998</v>
@@ -2305,36 +2253,36 @@
         <v>423066.01</v>
       </c>
       <c r="H31" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I31" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J31" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L31">
         <v>2023</v>
       </c>
       <c r="M31" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="N31">
         <v>48.295206621004567</v>
       </c>
       <c r="O31" t="s">
-        <v>41</v>
-      </c>
-      <c r="P31" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
+      </c>
+      <c r="P31" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="32" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B32" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="C32" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D32">
         <v>38.4266767746672</v>
@@ -2346,36 +2294,36 @@
         <v>637071.14593878668</v>
       </c>
       <c r="H32" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I32" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J32" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L32">
         <v>2025</v>
       </c>
       <c r="M32" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="N32">
         <v>72.725016659678843</v>
       </c>
       <c r="O32" t="s">
-        <v>20</v>
-      </c>
-      <c r="P32" s="3" t="s">
-        <v>41</v>
+        <v>21</v>
+      </c>
+      <c r="P32" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="33" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B33" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="C33" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D33">
         <v>31.141703251211499</v>
@@ -2387,36 +2335,36 @@
         <v>445040.90318066528</v>
       </c>
       <c r="H33" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I33" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J33" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L33">
         <v>2025</v>
       </c>
       <c r="M33" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="N33">
         <v>50.803756070852209</v>
       </c>
       <c r="O33" t="s">
-        <v>20</v>
-      </c>
-      <c r="P33" s="3" t="s">
-        <v>41</v>
+        <v>21</v>
+      </c>
+      <c r="P33" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="34" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B34" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="C34" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D34">
         <v>43.420110000000001</v>
@@ -2428,36 +2376,36 @@
         <v>312000</v>
       </c>
       <c r="H34" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I34" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J34" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L34">
         <v>2024</v>
       </c>
       <c r="M34" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="N34">
         <v>35.61643835616438</v>
       </c>
       <c r="O34" t="s">
-        <v>20</v>
-      </c>
-      <c r="P34" s="3" t="s">
-        <v>41</v>
+        <v>21</v>
+      </c>
+      <c r="P34" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="35" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B35" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="C35" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D35">
         <v>38.727834458232799</v>
@@ -2469,36 +2417,36 @@
         <v>257755.10755995769</v>
       </c>
       <c r="H35" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I35" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J35" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L35">
         <v>2025</v>
       </c>
       <c r="M35" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="N35">
         <v>29.424099036524861</v>
       </c>
       <c r="O35" t="s">
-        <v>20</v>
-      </c>
-      <c r="P35" s="3" t="s">
-        <v>41</v>
+        <v>21</v>
+      </c>
+      <c r="P35" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="36" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B36" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="C36" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D36">
         <v>36.690885291978802</v>
@@ -2510,36 +2458,36 @@
         <v>201371.17778121689</v>
       </c>
       <c r="H36" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I36" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J36" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L36">
         <v>2025</v>
       </c>
       <c r="M36" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="N36">
         <v>22.987577372285038</v>
       </c>
       <c r="O36" t="s">
-        <v>20</v>
-      </c>
-      <c r="P36" s="3" t="s">
-        <v>41</v>
+        <v>21</v>
+      </c>
+      <c r="P36" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="37" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B37" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="C37" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D37">
         <v>34.972277654515203</v>
@@ -2551,36 +2499,36 @@
         <v>599688.7049220067</v>
       </c>
       <c r="H37" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I37" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J37" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L37">
         <v>2025</v>
       </c>
       <c r="M37" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="N37">
         <v>68.457614717124059</v>
       </c>
       <c r="O37" t="s">
-        <v>20</v>
-      </c>
-      <c r="P37" s="3" t="s">
-        <v>41</v>
+        <v>21</v>
+      </c>
+      <c r="P37" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="38" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B38" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="C38" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D38">
         <v>39.8638011379185</v>
@@ -2592,36 +2540,36 @@
         <v>1773286.7549579451</v>
       </c>
       <c r="H38" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I38" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J38" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L38">
         <v>2025</v>
       </c>
       <c r="M38" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="N38">
         <v>202.42999485821289</v>
       </c>
       <c r="O38" t="s">
-        <v>20</v>
-      </c>
-      <c r="P38" s="3" t="s">
-        <v>41</v>
+        <v>21</v>
+      </c>
+      <c r="P38" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="39" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B39" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="C39" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D39">
         <v>41.503774444497097</v>
@@ -2633,36 +2581,36 @@
         <v>432440.56989697582</v>
       </c>
       <c r="H39" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I39" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J39" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L39">
         <v>2025</v>
       </c>
       <c r="M39" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="N39">
         <v>49.365361860385363</v>
       </c>
       <c r="O39" t="s">
-        <v>20</v>
-      </c>
-      <c r="P39" s="3" t="s">
-        <v>41</v>
+        <v>21</v>
+      </c>
+      <c r="P39" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="40" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B40" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C40" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D40">
         <v>36.966500000000003</v>
@@ -2674,36 +2622,36 @@
         <v>749000</v>
       </c>
       <c r="H40" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I40" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J40" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L40">
         <v>2024</v>
       </c>
       <c r="M40" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="N40">
         <v>85.502283105022826</v>
       </c>
       <c r="O40" t="s">
-        <v>20</v>
-      </c>
-      <c r="P40" s="3" t="s">
-        <v>41</v>
+        <v>21</v>
+      </c>
+      <c r="P40" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="41" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B41" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="C41" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D41">
         <v>36.716600999999997</v>
@@ -2715,36 +2663,36 @@
         <v>613000</v>
       </c>
       <c r="H41" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I41" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J41" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L41">
         <v>2024</v>
       </c>
       <c r="M41" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="N41">
         <v>69.977168949771695</v>
       </c>
       <c r="O41" t="s">
-        <v>20</v>
-      </c>
-      <c r="P41" s="3" t="s">
-        <v>41</v>
+        <v>21</v>
+      </c>
+      <c r="P41" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="42" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B42" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="C42" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D42">
         <v>41.477659000000003</v>
@@ -2756,36 +2704,36 @@
         <v>424000</v>
       </c>
       <c r="H42" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I42" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J42" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L42">
         <v>2024</v>
       </c>
       <c r="M42" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="N42">
         <v>48.401826484018272</v>
       </c>
       <c r="O42" t="s">
-        <v>20</v>
-      </c>
-      <c r="P42" s="3" t="s">
-        <v>41</v>
+        <v>21</v>
+      </c>
+      <c r="P42" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="43" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B43" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="C43" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D43">
         <v>43.792389999999997</v>
@@ -2797,36 +2745,36 @@
         <v>391000</v>
       </c>
       <c r="H43" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I43" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J43" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L43">
         <v>2024</v>
       </c>
       <c r="M43" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="N43">
         <v>44.634703196347033</v>
       </c>
       <c r="O43" t="s">
-        <v>20</v>
-      </c>
-      <c r="P43" s="3" t="s">
-        <v>41</v>
+        <v>21</v>
+      </c>
+      <c r="P43" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="44" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B44" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="C44" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D44">
         <v>45.684699999999999</v>
@@ -2838,36 +2786,36 @@
         <v>722839</v>
       </c>
       <c r="H44" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I44" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J44" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L44">
         <v>2023</v>
       </c>
       <c r="M44" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
       <c r="N44">
         <v>82.515867579908672</v>
       </c>
       <c r="O44" t="s">
-        <v>41</v>
-      </c>
-      <c r="P44" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="45" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>22</v>
+      </c>
+      <c r="P44" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="45" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B45" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C45" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D45">
         <v>39.351709999999997</v>
@@ -2879,36 +2827,36 @@
         <v>1031000</v>
       </c>
       <c r="H45" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I45" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J45" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L45">
         <v>2024</v>
       </c>
       <c r="M45" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="N45">
         <v>117.6940639269406</v>
       </c>
       <c r="O45" t="s">
-        <v>20</v>
-      </c>
-      <c r="P45" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="P45" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="46" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B46" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C46" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D46">
         <v>44.671399999999998</v>
@@ -2920,36 +2868,36 @@
         <v>221172.83040000001</v>
       </c>
       <c r="H46" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I46" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J46" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L46">
         <v>2023</v>
       </c>
       <c r="M46" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="N46">
         <v>25.24804</v>
       </c>
       <c r="O46" t="s">
-        <v>41</v>
-      </c>
-      <c r="P46" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
+      </c>
+      <c r="P46" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="47" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B47" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="C47" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D47">
         <v>45.6111</v>
@@ -2961,36 +2909,36 @@
         <v>207266.76</v>
       </c>
       <c r="H47" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I47" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J47" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L47">
         <v>2023</v>
       </c>
       <c r="M47" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="N47">
         <v>23.660589041095889</v>
       </c>
       <c r="O47" t="s">
-        <v>41</v>
-      </c>
-      <c r="P47" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
+      </c>
+      <c r="P47" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="48" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B48" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="C48" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D48">
         <v>45.515300000000003</v>
@@ -3002,36 +2950,36 @@
         <v>808186</v>
       </c>
       <c r="H48" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I48" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J48" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L48">
         <v>2023</v>
       </c>
       <c r="M48" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="N48">
         <v>92.25867579908676</v>
       </c>
       <c r="O48" t="s">
-        <v>41</v>
-      </c>
-      <c r="P48" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
+      </c>
+      <c r="P48" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="49" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B49" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="C49" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D49">
         <v>39.666317999999997</v>
@@ -3043,36 +2991,36 @@
         <v>648000</v>
       </c>
       <c r="H49" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I49" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J49" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L49">
         <v>2024</v>
       </c>
       <c r="M49" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="N49">
         <v>73.972602739726028</v>
       </c>
       <c r="O49" t="s">
-        <v>20</v>
-      </c>
-      <c r="P49" s="3" t="s">
-        <v>41</v>
+        <v>21</v>
+      </c>
+      <c r="P49" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="50" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B50" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="C50" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D50">
         <v>38.750794080123498</v>
@@ -3084,36 +3032,36 @@
         <v>264345.06915039301</v>
       </c>
       <c r="H50" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I50" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J50" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L50">
         <v>2025</v>
       </c>
       <c r="M50" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="N50">
         <v>30.17637775689418</v>
       </c>
       <c r="O50" t="s">
-        <v>20</v>
-      </c>
-      <c r="P50" s="3" t="s">
-        <v>41</v>
+        <v>21</v>
+      </c>
+      <c r="P50" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="51" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B51" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="C51" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D51">
         <v>41.736699999999999</v>
@@ -3125,36 +3073,36 @@
         <v>326434</v>
       </c>
       <c r="H51" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I51" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J51" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L51">
         <v>2023</v>
       </c>
       <c r="M51" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="N51">
         <v>37.264155251141553</v>
       </c>
       <c r="O51" t="s">
-        <v>20</v>
-      </c>
-      <c r="P51" s="3" t="s">
-        <v>41</v>
+        <v>21</v>
+      </c>
+      <c r="P51" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="52" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B52" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="C52" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D52">
         <v>34.306566324113</v>
@@ -3166,36 +3114,36 @@
         <v>1037263.135995616</v>
       </c>
       <c r="H52" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I52" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J52" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L52">
         <v>2025</v>
       </c>
       <c r="M52" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
       <c r="N52">
         <v>118.4090337894539</v>
       </c>
       <c r="O52" t="s">
-        <v>20</v>
-      </c>
-      <c r="P52" s="3" t="s">
-        <v>41</v>
+        <v>21</v>
+      </c>
+      <c r="P52" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="53" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B53" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="C53" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D53">
         <v>45.049700000000001</v>
@@ -3207,36 +3155,36 @@
         <v>330208</v>
       </c>
       <c r="H53" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I53" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J53" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L53">
         <v>2023</v>
       </c>
       <c r="M53" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
       <c r="N53">
         <v>37.694977168949769</v>
       </c>
       <c r="O53" t="s">
-        <v>41</v>
-      </c>
-      <c r="P53" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
+      </c>
+      <c r="P53" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="54" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B54" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="C54" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D54">
         <v>45.408299999999997</v>
@@ -3248,36 +3196,36 @@
         <v>206634.7028</v>
       </c>
       <c r="H54" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I54" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J54" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L54">
         <v>2023</v>
       </c>
       <c r="M54" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="N54">
         <v>23.58843639269406</v>
       </c>
       <c r="O54" t="s">
-        <v>41</v>
-      </c>
-      <c r="P54" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
+      </c>
+      <c r="P54" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="55" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B55" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="C55" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D55">
         <v>45.504199999999997</v>
@@ -3289,36 +3237,36 @@
         <v>277838.32900000003</v>
       </c>
       <c r="H55" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I55" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J55" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L55">
         <v>2023</v>
       </c>
       <c r="M55" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
       <c r="N55">
         <v>31.716704223744291</v>
       </c>
       <c r="O55" t="s">
-        <v>41</v>
-      </c>
-      <c r="P55" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
+      </c>
+      <c r="P55" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="56" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B56" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C56" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D56">
         <v>36.735732350892</v>
@@ -3330,36 +3278,36 @@
         <v>6477157.1833037036</v>
       </c>
       <c r="H56" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I56" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J56" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L56">
         <v>2025</v>
       </c>
       <c r="M56" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="N56">
         <v>739.40150494334512</v>
       </c>
       <c r="O56" t="s">
-        <v>20</v>
-      </c>
-      <c r="P56" s="3" t="s">
-        <v>41</v>
+        <v>21</v>
+      </c>
+      <c r="P56" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="57" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B57" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="C57" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D57">
         <v>40.6753</v>
@@ -3371,36 +3319,36 @@
         <v>390621</v>
       </c>
       <c r="H57" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I57" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J57" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L57">
         <v>2023</v>
       </c>
       <c r="M57" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="N57">
         <v>44.591438356164382</v>
       </c>
       <c r="O57" t="s">
-        <v>20</v>
-      </c>
-      <c r="P57" s="3" t="s">
-        <v>41</v>
+        <v>21</v>
+      </c>
+      <c r="P57" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="58" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B58" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="C58" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D58">
         <v>38.190832999999998</v>
@@ -3412,36 +3360,36 @@
         <v>263673</v>
       </c>
       <c r="H58" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I58" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J58" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L58">
         <v>2023</v>
       </c>
       <c r="M58" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
       <c r="N58">
         <v>30.099657534246571</v>
       </c>
       <c r="O58" t="s">
-        <v>20</v>
-      </c>
-      <c r="P58" s="3" t="s">
-        <v>41</v>
+        <v>21</v>
+      </c>
+      <c r="P58" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="59" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B59" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="C59" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D59">
         <v>38.742497000573699</v>
@@ -3453,36 +3401,36 @@
         <v>201371.17778121689</v>
       </c>
       <c r="H59" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I59" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J59" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L59">
         <v>2025</v>
       </c>
       <c r="M59" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="N59">
         <v>22.987577372285038</v>
       </c>
       <c r="O59" t="s">
-        <v>20</v>
-      </c>
-      <c r="P59" s="3" t="s">
-        <v>41</v>
+        <v>21</v>
+      </c>
+      <c r="P59" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="60" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B60" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="C60" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D60">
         <v>43.022080000000003</v>
@@ -3494,36 +3442,36 @@
         <v>454000</v>
       </c>
       <c r="H60" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I60" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J60" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L60">
         <v>2024</v>
       </c>
       <c r="M60" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="N60">
         <v>51.826484018264843</v>
       </c>
       <c r="O60" t="s">
-        <v>20</v>
-      </c>
-      <c r="P60" s="3" t="s">
-        <v>41</v>
+        <v>21</v>
+      </c>
+      <c r="P60" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="61" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B61" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="C61" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D61">
         <v>45.2804</v>
@@ -3535,36 +3483,36 @@
         <v>254107</v>
       </c>
       <c r="H61" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I61" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J61" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L61">
         <v>2023</v>
       </c>
       <c r="M61" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="N61">
         <v>29.007648401826479</v>
       </c>
       <c r="O61" t="s">
-        <v>41</v>
-      </c>
-      <c r="P61" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
+      </c>
+      <c r="P61" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="62" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B62" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C62" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D62">
         <v>32.336415294557497</v>
@@ -3576,36 +3524,36 @@
         <v>1031558</v>
       </c>
       <c r="H62" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I62" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J62" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L62">
         <v>2025</v>
       </c>
       <c r="M62" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="N62">
         <v>117.7577625570776</v>
       </c>
       <c r="O62" t="s">
-        <v>20</v>
-      </c>
-      <c r="P62" s="3" t="s">
-        <v>41</v>
+        <v>21</v>
+      </c>
+      <c r="P62" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="63" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B63" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="C63" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D63">
         <v>36.781410300080097</v>
@@ -3617,36 +3565,36 @@
         <v>727575.77467714867</v>
       </c>
       <c r="H63" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I63" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J63" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L63">
         <v>2025</v>
       </c>
       <c r="M63" t="s">
-        <v>100</v>
+        <v>101</v>
       </c>
       <c r="N63">
         <v>83.056595282779526</v>
       </c>
       <c r="O63" t="s">
-        <v>20</v>
-      </c>
-      <c r="P63" s="3" t="s">
-        <v>41</v>
+        <v>21</v>
+      </c>
+      <c r="P63" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="64" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B64" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="C64" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D64">
         <v>32.6169677543662</v>
@@ -3658,36 +3606,36 @@
         <v>260534.99053302259</v>
       </c>
       <c r="H64" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I64" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J64" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L64">
         <v>2025</v>
       </c>
       <c r="M64" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
       <c r="N64">
         <v>29.741437275459202</v>
       </c>
       <c r="O64" t="s">
-        <v>20</v>
-      </c>
-      <c r="P64" s="3" t="s">
-        <v>41</v>
+        <v>21</v>
+      </c>
+      <c r="P64" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="65" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B65" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="C65" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D65">
         <v>41.419170999999999</v>
@@ -3699,36 +3647,36 @@
         <v>323000</v>
       </c>
       <c r="H65" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I65" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J65" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L65">
         <v>2024</v>
       </c>
       <c r="M65" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="N65">
         <v>36.87214611872146</v>
       </c>
       <c r="O65" t="s">
-        <v>20</v>
-      </c>
-      <c r="P65" s="3" t="s">
-        <v>41</v>
+        <v>21</v>
+      </c>
+      <c r="P65" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="66" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B66" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="C66" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D66">
         <v>44.967320000000001</v>
@@ -3740,36 +3688,36 @@
         <v>314000</v>
       </c>
       <c r="H66" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I66" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J66" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L66">
         <v>2024</v>
       </c>
       <c r="M66" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="N66">
         <v>35.844748858447488</v>
       </c>
       <c r="O66" t="s">
-        <v>20</v>
-      </c>
-      <c r="P66" s="3" t="s">
-        <v>41</v>
+        <v>21</v>
+      </c>
+      <c r="P66" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="67" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B67" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="C67" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D67">
         <v>36.903055999999999</v>
@@ -3781,36 +3729,36 @@
         <v>281353</v>
       </c>
       <c r="H67" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I67" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J67" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L67">
         <v>2023</v>
       </c>
       <c r="M67" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="N67">
         <v>32.117922374429227</v>
       </c>
       <c r="O67" t="s">
-        <v>20</v>
-      </c>
-      <c r="P67" s="3" t="s">
-        <v>41</v>
+        <v>21</v>
+      </c>
+      <c r="P67" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="68" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B68" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="C68" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D68">
         <v>31.916468054311501</v>
@@ -3822,36 +3770,36 @@
         <v>1155048.4074455709</v>
       </c>
       <c r="H68" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I68" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J68" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L68">
         <v>2025</v>
       </c>
       <c r="M68" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="N68">
         <v>131.85484103259941</v>
       </c>
       <c r="O68" t="s">
-        <v>20</v>
-      </c>
-      <c r="P68" s="3" t="s">
-        <v>41</v>
+        <v>21</v>
+      </c>
+      <c r="P68" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="69" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B69" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="C69" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D69">
         <v>40.5167</v>
@@ -3863,36 +3811,36 @@
         <v>4351958.3</v>
       </c>
       <c r="H69" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I69" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J69" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L69">
         <v>2023</v>
       </c>
       <c r="M69" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="N69">
         <v>496.79889269406391</v>
       </c>
       <c r="O69" t="s">
-        <v>20</v>
-      </c>
-      <c r="P69" s="3" t="s">
-        <v>41</v>
+        <v>21</v>
+      </c>
+      <c r="P69" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="70" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B70" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="C70" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D70">
         <v>36.933010275675301</v>
@@ -3904,36 +3852,36 @@
         <v>531302.09106205474</v>
       </c>
       <c r="H70" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I70" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J70" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L70">
         <v>2025</v>
       </c>
       <c r="M70" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="N70">
         <v>60.650923637220863</v>
       </c>
       <c r="O70" t="s">
-        <v>20</v>
-      </c>
-      <c r="P70" s="3" t="s">
-        <v>41</v>
+        <v>21</v>
+      </c>
+      <c r="P70" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="71" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B71" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="C71" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D71">
         <v>33.628254108861398</v>
@@ -3945,36 +3893,36 @@
         <v>413849.33665999997</v>
       </c>
       <c r="H71" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I71" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J71" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L71">
         <v>2025</v>
       </c>
       <c r="M71" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
       <c r="N71">
         <v>47.243074961187212</v>
       </c>
       <c r="O71" t="s">
-        <v>20</v>
-      </c>
-      <c r="P71" s="3" t="s">
-        <v>41</v>
+        <v>21</v>
+      </c>
+      <c r="P71" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="72" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B72" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="C72" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D72">
         <v>36.2630234976574</v>
@@ -3986,36 +3934,36 @@
         <v>2035690.794484779</v>
       </c>
       <c r="H72" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I72" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J72" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L72">
         <v>2025</v>
       </c>
       <c r="M72" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="N72">
         <v>232.38479389095659</v>
       </c>
       <c r="O72" t="s">
-        <v>20</v>
-      </c>
-      <c r="P72" s="3" t="s">
-        <v>41</v>
+        <v>21</v>
+      </c>
+      <c r="P72" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="73" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B73" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
       <c r="C73" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D73">
         <v>43.363599999999998</v>
@@ -4027,36 +3975,36 @@
         <v>482587</v>
       </c>
       <c r="H73" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I73" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J73" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L73">
         <v>2023</v>
       </c>
       <c r="M73" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="N73">
         <v>55.089840182648402</v>
       </c>
       <c r="O73" t="s">
-        <v>20</v>
-      </c>
-      <c r="P73" s="3" t="s">
-        <v>41</v>
+        <v>21</v>
+      </c>
+      <c r="P73" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="74" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B74" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="C74" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D74">
         <v>37.770531602188598</v>
@@ -4068,36 +4016,36 @@
         <v>1830468.2922518109</v>
       </c>
       <c r="H74" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I74" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J74" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L74">
         <v>2025</v>
       </c>
       <c r="M74" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="N74">
         <v>208.9575676086543</v>
       </c>
       <c r="O74" t="s">
-        <v>20</v>
-      </c>
-      <c r="P74" s="3" t="s">
-        <v>41</v>
+        <v>21</v>
+      </c>
+      <c r="P74" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="75" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B75" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="C75" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D75">
         <v>40.966700000000003</v>
@@ -4109,36 +4057,36 @@
         <v>393166.2671</v>
       </c>
       <c r="H75" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I75" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J75" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L75">
         <v>2023</v>
       </c>
       <c r="M75" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="N75">
         <v>44.881993961187213</v>
       </c>
       <c r="O75" t="s">
-        <v>20</v>
-      </c>
-      <c r="P75" s="3" t="s">
-        <v>41</v>
+        <v>21</v>
+      </c>
+      <c r="P75" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="76" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B76" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="C76" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D76">
         <v>39.644351</v>
@@ -4150,36 +4098,36 @@
         <v>560000</v>
       </c>
       <c r="H76" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I76" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J76" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L76">
         <v>2024</v>
       </c>
       <c r="M76" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
       <c r="N76">
         <v>63.926940639269397</v>
       </c>
       <c r="O76" t="s">
-        <v>20</v>
-      </c>
-      <c r="P76" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="77" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>21</v>
+      </c>
+      <c r="P76" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="77" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B77" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C77" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D77">
         <v>38.335569999999997</v>
@@ -4191,36 +4139,36 @@
         <v>552000</v>
       </c>
       <c r="H77" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I77" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J77" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L77">
         <v>2024</v>
       </c>
       <c r="M77" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="N77">
         <v>63.013698630136993</v>
       </c>
       <c r="O77" t="s">
-        <v>41</v>
-      </c>
-      <c r="P77" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="78" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>22</v>
+      </c>
+      <c r="P77" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="78" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B78" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="C78" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D78">
         <v>38.130180000000003</v>
@@ -4232,36 +4180,36 @@
         <v>1186000</v>
       </c>
       <c r="H78" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I78" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J78" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L78">
         <v>2024</v>
       </c>
       <c r="M78" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
       <c r="N78">
         <v>135.38812785388129</v>
       </c>
       <c r="O78" t="s">
-        <v>41</v>
-      </c>
-      <c r="P78" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="79" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>22</v>
+      </c>
+      <c r="P78" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="79" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B79" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="C79" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D79">
         <v>40.699100000000001</v>
@@ -4273,36 +4221,36 @@
         <v>606000</v>
       </c>
       <c r="H79" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I79" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J79" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L79">
         <v>2024</v>
       </c>
       <c r="M79" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="N79">
         <v>69.178082191780817</v>
       </c>
       <c r="O79" t="s">
-        <v>41</v>
-      </c>
-      <c r="P79" s="3" t="s">
-        <v>20</v>
+        <v>22</v>
+      </c>
+      <c r="P79" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="80" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B80" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
       <c r="C80" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D80">
         <v>43.541710000000002</v>
@@ -4314,36 +4262,36 @@
         <v>544000</v>
       </c>
       <c r="H80" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I80" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J80" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L80">
         <v>2024</v>
       </c>
       <c r="M80" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="N80">
         <v>62.100456621004568</v>
       </c>
       <c r="O80" t="s">
-        <v>20</v>
-      </c>
-      <c r="P80" s="3" t="s">
-        <v>41</v>
+        <v>21</v>
+      </c>
+      <c r="P80" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="81" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B81" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="C81" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D81">
         <v>45.642499999999998</v>
@@ -4355,36 +4303,36 @@
         <v>402532.05</v>
       </c>
       <c r="H81" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I81" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J81" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L81">
         <v>2023</v>
       </c>
       <c r="M81" t="s">
-        <v>122</v>
+        <v>123</v>
       </c>
       <c r="N81">
         <v>45.95114726027397</v>
       </c>
       <c r="O81" t="s">
-        <v>20</v>
-      </c>
-      <c r="P81" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="P81" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="82" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B82" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="C82" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D82">
         <v>45.788600000000002</v>
@@ -4396,36 +4344,36 @@
         <v>231572</v>
       </c>
       <c r="H82" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I82" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J82" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L82">
         <v>2023</v>
       </c>
       <c r="M82" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
       <c r="N82">
         <v>26.4351598173516</v>
       </c>
       <c r="O82" t="s">
-        <v>20</v>
-      </c>
-      <c r="P82" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="P82" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="83" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B83" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="C83" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D83">
         <v>45.459400000000002</v>
@@ -4437,36 +4385,36 @@
         <v>203439</v>
       </c>
       <c r="H83" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I83" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J83" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L83">
         <v>2023</v>
       </c>
       <c r="M83" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="N83">
         <v>23.223630136986301</v>
       </c>
       <c r="O83" t="s">
-        <v>20</v>
-      </c>
-      <c r="P83" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="P83" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="84" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B84" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="C84" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D84">
         <v>41.4375</v>
@@ -4478,36 +4426,36 @@
         <v>380667</v>
       </c>
       <c r="H84" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I84" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J84" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L84">
         <v>2023</v>
       </c>
       <c r="M84" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="N84">
         <v>43.455136986301369</v>
       </c>
       <c r="O84" t="s">
-        <v>20</v>
-      </c>
-      <c r="P84" s="3" t="s">
-        <v>41</v>
+        <v>21</v>
+      </c>
+      <c r="P84" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="85" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B85" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C85" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D85">
         <v>34.721699999999998</v>
@@ -4519,36 +4467,36 @@
         <v>1370000</v>
       </c>
       <c r="H85" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I85" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J85" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L85">
         <v>2023</v>
       </c>
       <c r="M85" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="N85">
         <v>156.39269406392691</v>
       </c>
       <c r="O85" t="s">
-        <v>20</v>
-      </c>
-      <c r="P85" s="3" t="s">
-        <v>41</v>
+        <v>21</v>
+      </c>
+      <c r="P85" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="86" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B86" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="C86" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D86">
         <v>43.768630000000002</v>
@@ -4560,36 +4508,36 @@
         <v>434000</v>
       </c>
       <c r="H86" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I86" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J86" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L86">
         <v>2024</v>
       </c>
       <c r="M86" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="N86">
         <v>49.543378995433791</v>
       </c>
       <c r="O86" t="s">
-        <v>20</v>
-      </c>
-      <c r="P86" s="3" t="s">
-        <v>41</v>
+        <v>21</v>
+      </c>
+      <c r="P86" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="87" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B87" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="C87" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D87">
         <v>36.964332544555901</v>
@@ -4601,36 +4549,36 @@
         <v>2114795.906676</v>
       </c>
       <c r="H87" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="I87" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J87" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L87">
         <v>2025</v>
       </c>
       <c r="M87" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="N87">
         <v>241.41505783972599</v>
       </c>
       <c r="O87" t="s">
-        <v>20</v>
-      </c>
-      <c r="P87" s="3" t="s">
-        <v>41</v>
+        <v>21</v>
+      </c>
+      <c r="P87" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="88" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B88" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="C88" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D88">
         <v>43.136479999999999</v>
@@ -4642,36 +4590,36 @@
         <v>201000</v>
       </c>
       <c r="H88" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="I88" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="J88" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L88">
         <v>2024</v>
       </c>
       <c r="M88" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="N88">
         <v>22.94520547945206</v>
       </c>
       <c r="O88" t="s">
-        <v>20</v>
-      </c>
-      <c r="P88" s="3" t="s">
-        <v>41</v>
+        <v>21</v>
+      </c>
+      <c r="P88" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="89" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B89" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="C89" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D89">
         <v>38.740041692079899</v>
@@ -4683,39 +4631,39 @@
         <v>216156.41968828891</v>
       </c>
       <c r="H89" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="I89" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="J89" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="L89">
         <v>2025</v>
       </c>
       <c r="M89" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
       <c r="N89">
         <v>24.675390375375439</v>
       </c>
       <c r="O89" t="s">
-        <v>20</v>
-      </c>
-      <c r="P89" s="3" t="s">
-        <v>41</v>
+        <v>21</v>
+      </c>
+      <c r="P89" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="90" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>133</v>
+        <v>134</v>
       </c>
       <c r="B90" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
       <c r="C90" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D90">
         <v>31.9725</v>
@@ -4727,30 +4675,30 @@
         <v>398430000</v>
       </c>
       <c r="I90" t="s">
+        <v>136</v>
+      </c>
+      <c r="J90" t="s">
+        <v>137</v>
+      </c>
+      <c r="M90" t="s">
         <v>135</v>
       </c>
-      <c r="J90" t="s">
-        <v>136</v>
-      </c>
-      <c r="M90" t="s">
-        <v>134</v>
-      </c>
       <c r="O90" t="s">
-        <v>20</v>
-      </c>
-      <c r="P90" s="3" t="s">
-        <v>41</v>
+        <v>21</v>
+      </c>
+      <c r="P90" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="91" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B91" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="C91" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D91">
         <v>31.617999999999999</v>
@@ -4762,30 +4710,30 @@
         <v>179110000</v>
       </c>
       <c r="I91" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="J91" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M91" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="O91" t="s">
-        <v>20</v>
-      </c>
-      <c r="P91" s="3" t="s">
-        <v>41</v>
+        <v>21</v>
+      </c>
+      <c r="P91" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="92" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B92" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
       <c r="C92" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D92">
         <v>40.716999999999999</v>
@@ -4797,30 +4745,30 @@
         <v>54000000</v>
       </c>
       <c r="I92" t="s">
+        <v>142</v>
+      </c>
+      <c r="J92" t="s">
+        <v>137</v>
+      </c>
+      <c r="M92" t="s">
         <v>141</v>
       </c>
-      <c r="J92" t="s">
-        <v>136</v>
-      </c>
-      <c r="M92" t="s">
-        <v>140</v>
-      </c>
       <c r="O92" t="s">
-        <v>20</v>
-      </c>
-      <c r="P92" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="93" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>21</v>
+      </c>
+      <c r="P92" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="93" spans="1:16" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
       <c r="B93" t="s">
-        <v>143</v>
+        <v>144</v>
       </c>
       <c r="C93" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D93">
         <v>40.802035296804902</v>
@@ -4832,30 +4780,30 @@
         <v>66400000.000000007</v>
       </c>
       <c r="I93" t="s">
+        <v>145</v>
+      </c>
+      <c r="J93" t="s">
+        <v>137</v>
+      </c>
+      <c r="M93" t="s">
         <v>144</v>
       </c>
-      <c r="J93" t="s">
-        <v>136</v>
-      </c>
-      <c r="M93" t="s">
-        <v>143</v>
-      </c>
       <c r="O93" t="s">
-        <v>20</v>
-      </c>
-      <c r="P93" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="P93" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="94" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B94" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
       <c r="C94" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D94">
         <v>43.601553631123352</v>
@@ -4867,30 +4815,30 @@
         <v>444985000</v>
       </c>
       <c r="I94" t="s">
+        <v>148</v>
+      </c>
+      <c r="J94" t="s">
+        <v>137</v>
+      </c>
+      <c r="M94" t="s">
         <v>147</v>
       </c>
-      <c r="J94" t="s">
-        <v>136</v>
-      </c>
-      <c r="M94" t="s">
-        <v>146</v>
-      </c>
       <c r="O94" t="s">
-        <v>20</v>
-      </c>
-      <c r="P94" s="3" t="s">
-        <v>41</v>
+        <v>21</v>
+      </c>
+      <c r="P94" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="95" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="B95" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C95" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D95">
         <v>44.387</v>
@@ -4902,30 +4850,30 @@
         <v>515000000</v>
       </c>
       <c r="I95" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="J95" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="M95" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="O95" t="s">
-        <v>20</v>
-      </c>
-      <c r="P95" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="P95" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="96" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>150</v>
+        <v>151</v>
       </c>
       <c r="B96" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C96" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D96">
         <v>39.114235999999998</v>
@@ -4937,27 +4885,27 @@
         <v>130000000</v>
       </c>
       <c r="I96" t="s">
+        <v>153</v>
+      </c>
+      <c r="J96" t="s">
+        <v>137</v>
+      </c>
+      <c r="M96" t="s">
         <v>152</v>
       </c>
-      <c r="J96" t="s">
-        <v>136</v>
-      </c>
-      <c r="M96" t="s">
-        <v>151</v>
-      </c>
       <c r="O96" t="s">
-        <v>20</v>
-      </c>
-      <c r="P96" s="3" t="s">
-        <v>41</v>
+        <v>21</v>
+      </c>
+      <c r="P96" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="97" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B97" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C97" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D97">
         <v>38.333333000000003</v>
@@ -4966,27 +4914,27 @@
         <v>-0.48333300000000001</v>
       </c>
       <c r="J97" t="s">
+        <v>155</v>
+      </c>
+      <c r="K97" t="s">
+        <v>156</v>
+      </c>
+      <c r="M97" t="s">
         <v>154</v>
       </c>
-      <c r="K97" t="s">
-        <v>155</v>
-      </c>
-      <c r="M97" t="s">
-        <v>153</v>
-      </c>
       <c r="O97" t="s">
-        <v>20</v>
-      </c>
-      <c r="P97" s="3" t="s">
-        <v>41</v>
+        <v>21</v>
+      </c>
+      <c r="P97" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="98" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B98" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C98" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D98">
         <v>43.628999999999998</v>
@@ -4995,27 +4943,27 @@
         <v>13.494</v>
       </c>
       <c r="J98" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K98" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M98" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="O98" t="s">
-        <v>20</v>
-      </c>
-      <c r="P98" s="3" t="s">
-        <v>41</v>
+        <v>21</v>
+      </c>
+      <c r="P98" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="99" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B99" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="C99" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="D99">
         <v>31.816666999999999</v>
@@ -5024,27 +4972,27 @@
         <v>34.65</v>
       </c>
       <c r="J99" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K99" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M99" t="s">
-        <v>157</v>
+        <v>158</v>
       </c>
       <c r="O99" t="s">
-        <v>20</v>
-      </c>
-      <c r="P99" s="3" t="s">
-        <v>41</v>
+        <v>21</v>
+      </c>
+      <c r="P99" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="100" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B100" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="C100" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D100">
         <v>37.216667000000001</v>
@@ -5053,27 +5001,27 @@
         <v>15.233333</v>
       </c>
       <c r="J100" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K100" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M100" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
       <c r="O100" t="s">
-        <v>20</v>
-      </c>
-      <c r="P100" s="3" t="s">
-        <v>41</v>
+        <v>21</v>
+      </c>
+      <c r="P100" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="101" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B101" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="C101" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D101">
         <v>32.116667</v>
@@ -5082,27 +5030,27 @@
         <v>20.05</v>
       </c>
       <c r="J101" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K101" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M101" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="O101" t="s">
-        <v>20</v>
-      </c>
-      <c r="P101" s="3" t="s">
-        <v>41</v>
+        <v>21</v>
+      </c>
+      <c r="P101" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="102" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B102" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="C102" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D102">
         <v>36.883333</v>
@@ -5111,27 +5059,27 @@
         <v>35.933332999999998</v>
       </c>
       <c r="J102" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K102" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M102" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="O102" t="s">
-        <v>20</v>
-      </c>
-      <c r="P102" s="3" t="s">
-        <v>41</v>
+        <v>21</v>
+      </c>
+      <c r="P102" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="103" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B103" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="C103" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D103">
         <v>31.266667000000002</v>
@@ -5140,27 +5088,27 @@
         <v>32.299999999999997</v>
       </c>
       <c r="J103" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K103" t="s">
+        <v>163</v>
+      </c>
+      <c r="M103" t="s">
         <v>162</v>
       </c>
-      <c r="M103" t="s">
-        <v>161</v>
-      </c>
       <c r="O103" t="s">
-        <v>20</v>
-      </c>
-      <c r="P103" s="3" t="s">
-        <v>41</v>
+        <v>21</v>
+      </c>
+      <c r="P103" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="104" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B104" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="C104" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D104">
         <v>44.553930999999999</v>
@@ -5169,27 +5117,27 @@
         <v>12.264552999999999</v>
       </c>
       <c r="J104" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K104" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M104" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="O104" t="s">
-        <v>20</v>
-      </c>
-      <c r="P104" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="P104" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="105" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B105" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="C105" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D105">
         <v>42.101999999999997</v>
@@ -5198,27 +5146,27 @@
         <v>11.771000000000001</v>
       </c>
       <c r="J105" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K105" t="s">
+        <v>166</v>
+      </c>
+      <c r="M105" t="s">
         <v>165</v>
       </c>
-      <c r="M105" t="s">
-        <v>164</v>
-      </c>
       <c r="O105" t="s">
-        <v>20</v>
-      </c>
-      <c r="P105" s="3" t="s">
-        <v>41</v>
+        <v>21</v>
+      </c>
+      <c r="P105" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="106" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B106" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="C106" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D106">
         <v>39.078000000000003</v>
@@ -5227,27 +5175,27 @@
         <v>17.135999999999999</v>
       </c>
       <c r="J106" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K106" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M106" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
       <c r="O106" t="s">
-        <v>20</v>
-      </c>
-      <c r="P106" s="3" t="s">
-        <v>41</v>
+        <v>21</v>
+      </c>
+      <c r="P106" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="107" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B107" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="C107" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D107">
         <v>32.766666999999998</v>
@@ -5256,27 +5204,27 @@
         <v>22.65</v>
       </c>
       <c r="J107" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K107" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M107" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="O107" t="s">
-        <v>20</v>
-      </c>
-      <c r="P107" s="3" t="s">
-        <v>41</v>
+        <v>21</v>
+      </c>
+      <c r="P107" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="108" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B108" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="C108" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D108">
         <v>36.966500000000003</v>
@@ -5285,27 +5233,27 @@
         <v>-1.9029</v>
       </c>
       <c r="J108" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K108" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M108" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
       <c r="O108" t="s">
-        <v>20</v>
-      </c>
-      <c r="P108" s="3" t="s">
-        <v>41</v>
+        <v>21</v>
+      </c>
+      <c r="P108" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="109" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B109" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="C109" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D109">
         <v>43.416666999999997</v>
@@ -5314,27 +5262,27 @@
         <v>4.8833330000000004</v>
       </c>
       <c r="J109" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K109" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M109" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
       <c r="O109" t="s">
-        <v>20</v>
-      </c>
-      <c r="P109" s="3" t="s">
-        <v>41</v>
+        <v>21</v>
+      </c>
+      <c r="P109" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="110" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B110" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="C110" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D110">
         <v>44.398000000000003</v>
@@ -5343,27 +5291,27 @@
         <v>8.9220000000000006</v>
       </c>
       <c r="J110" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K110" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M110" t="s">
-        <v>169</v>
+        <v>170</v>
       </c>
       <c r="O110" t="s">
-        <v>20</v>
-      </c>
-      <c r="P110" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="111" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>21</v>
+      </c>
+      <c r="P110" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="111" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B111" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="C111" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D111">
         <v>39.351709999999997</v>
@@ -5372,27 +5320,27 @@
         <v>22.984500000000001</v>
       </c>
       <c r="J111" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K111" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M111" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="O111" t="s">
-        <v>20</v>
-      </c>
-      <c r="P111" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="P111" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="112" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B112" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="C112" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D112">
         <v>36.735732349999999</v>
@@ -5401,27 +5349,27 @@
         <v>36.209483480000003</v>
       </c>
       <c r="J112" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K112" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M112" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="O112" t="s">
-        <v>20</v>
-      </c>
-      <c r="P112" s="3" t="s">
-        <v>41</v>
+        <v>21</v>
+      </c>
+      <c r="P112" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="113" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B113" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="C113" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D113">
         <v>38.433332999999998</v>
@@ -5430,27 +5378,27 @@
         <v>27.133333</v>
       </c>
       <c r="J113" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K113" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M113" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="O113" t="s">
-        <v>20</v>
-      </c>
-      <c r="P113" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="114" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>21</v>
+      </c>
+      <c r="P113" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="114" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B114" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="C114" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D114">
         <v>40.933332999999998</v>
@@ -5459,27 +5407,27 @@
         <v>24.4</v>
       </c>
       <c r="J114" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K114" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M114" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="O114" t="s">
-        <v>20</v>
-      </c>
-      <c r="P114" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="P114" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="115" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B115" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="C115" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D115">
         <v>32.666666999999997</v>
@@ -5488,27 +5436,27 @@
         <v>14.25</v>
       </c>
       <c r="J115" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K115" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M115" t="s">
-        <v>172</v>
+        <v>173</v>
       </c>
       <c r="O115" t="s">
-        <v>20</v>
-      </c>
-      <c r="P115" s="3" t="s">
-        <v>41</v>
+        <v>21</v>
+      </c>
+      <c r="P115" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="116" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B116" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="C116" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D116">
         <v>44.967300000000002</v>
@@ -5517,27 +5465,27 @@
         <v>14.118499999999999</v>
       </c>
       <c r="J116" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K116" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M116" t="s">
-        <v>173</v>
+        <v>174</v>
       </c>
       <c r="O116" t="s">
-        <v>20</v>
-      </c>
-      <c r="P116" s="3" t="s">
-        <v>41</v>
+        <v>21</v>
+      </c>
+      <c r="P116" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="117" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B117" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="C117" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D117">
         <v>37.866667</v>
@@ -5546,27 +5494,27 @@
         <v>27.25</v>
       </c>
       <c r="J117" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K117" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M117" t="s">
-        <v>174</v>
+        <v>175</v>
       </c>
       <c r="O117" t="s">
-        <v>20</v>
-      </c>
-      <c r="P117" s="3" t="s">
-        <v>41</v>
+        <v>21</v>
+      </c>
+      <c r="P117" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="118" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B118" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="C118" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D118">
         <v>36.716667000000001</v>
@@ -5575,27 +5523,27 @@
         <v>-4.4166670000000003</v>
       </c>
       <c r="J118" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K118" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M118" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="O118" t="s">
-        <v>20</v>
-      </c>
-      <c r="P118" s="3" t="s">
-        <v>41</v>
+        <v>21</v>
+      </c>
+      <c r="P118" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="119" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B119" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="C119" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D119">
         <v>36.799999999999997</v>
@@ -5604,27 +5552,27 @@
         <v>34.633333</v>
       </c>
       <c r="J119" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K119" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M119" t="s">
-        <v>176</v>
+        <v>177</v>
       </c>
       <c r="O119" t="s">
-        <v>20</v>
-      </c>
-      <c r="P119" s="3" t="s">
-        <v>41</v>
+        <v>21</v>
+      </c>
+      <c r="P119" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="120" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B120" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="C120" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D120">
         <v>45.783332999999999</v>
@@ -5633,27 +5581,27 @@
         <v>13.55</v>
       </c>
       <c r="J120" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K120" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M120" t="s">
-        <v>177</v>
+        <v>178</v>
       </c>
       <c r="O120" t="s">
-        <v>20</v>
-      </c>
-      <c r="P120" s="3" t="s">
-        <v>41</v>
+        <v>21</v>
+      </c>
+      <c r="P120" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="121" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B121" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C121" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D121">
         <v>40.832999999999998</v>
@@ -5662,27 +5610,27 @@
         <v>14.275</v>
       </c>
       <c r="J121" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K121" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M121" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="O121" t="s">
-        <v>20</v>
-      </c>
-      <c r="P121" s="3" t="s">
-        <v>41</v>
+        <v>21</v>
+      </c>
+      <c r="P121" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="122" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B122" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C122" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D122">
         <v>38.766666999999998</v>
@@ -5691,27 +5639,27 @@
         <v>26.916667</v>
       </c>
       <c r="J122" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K122" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M122" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="O122" t="s">
-        <v>20</v>
-      </c>
-      <c r="P122" s="3" t="s">
-        <v>41</v>
+        <v>21</v>
+      </c>
+      <c r="P122" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="123" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B123" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C123" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D123">
         <v>39.566667000000002</v>
@@ -5720,27 +5668,27 @@
         <v>2.6333329999999999</v>
       </c>
       <c r="J123" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K123" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M123" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="O123" t="s">
-        <v>20</v>
-      </c>
-      <c r="P123" s="3" t="s">
-        <v>41</v>
+        <v>21</v>
+      </c>
+      <c r="P123" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="124" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B124" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="C124" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D124">
         <v>43.016666999999998</v>
@@ -5749,27 +5697,27 @@
         <v>3.0666669999999998</v>
       </c>
       <c r="J124" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K124" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M124" t="s">
-        <v>181</v>
+        <v>182</v>
       </c>
       <c r="O124" t="s">
-        <v>20</v>
-      </c>
-      <c r="P124" s="3" t="s">
-        <v>41</v>
+        <v>21</v>
+      </c>
+      <c r="P124" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="125" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B125" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="C125" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D125">
         <v>41.334000000000003</v>
@@ -5778,27 +5726,27 @@
         <v>16.292000000000002</v>
       </c>
       <c r="J125" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K125" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M125" t="s">
-        <v>182</v>
+        <v>183</v>
       </c>
       <c r="O125" t="s">
-        <v>20</v>
-      </c>
-      <c r="P125" s="3" t="s">
-        <v>41</v>
+        <v>21</v>
+      </c>
+      <c r="P125" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="126" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B126" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="C126" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D126">
         <v>45.416666999999997</v>
@@ -5807,27 +5755,27 @@
         <v>12.433332999999999</v>
       </c>
       <c r="J126" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K126" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M126" t="s">
-        <v>183</v>
+        <v>184</v>
       </c>
       <c r="O126" t="s">
-        <v>20</v>
-      </c>
-      <c r="P126" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="P126" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="127" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B127" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="C127" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D127">
         <v>38.119</v>
@@ -5836,27 +5784,27 @@
         <v>13.38</v>
       </c>
       <c r="J127" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K127" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M127" t="s">
-        <v>184</v>
+        <v>185</v>
       </c>
       <c r="O127" t="s">
-        <v>20</v>
-      </c>
-      <c r="P127" s="3" t="s">
-        <v>41</v>
+        <v>21</v>
+      </c>
+      <c r="P127" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="128" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B128" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="C128" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D128">
         <v>41.383333329999999</v>
@@ -5865,27 +5813,27 @@
         <v>19.416666670000001</v>
       </c>
       <c r="J128" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K128" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M128" t="s">
-        <v>185</v>
+        <v>186</v>
       </c>
       <c r="O128" t="s">
-        <v>20</v>
-      </c>
-      <c r="P128" s="3" t="s">
-        <v>41</v>
+        <v>21</v>
+      </c>
+      <c r="P128" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="129" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B129" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="C129" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D129">
         <v>36.716667000000001</v>
@@ -5894,27 +5842,27 @@
         <v>14.85</v>
       </c>
       <c r="J129" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K129" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M129" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="O129" t="s">
-        <v>20</v>
-      </c>
-      <c r="P129" s="3" t="s">
-        <v>41</v>
+        <v>21</v>
+      </c>
+      <c r="P129" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="130" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B130" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="C130" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D130">
         <v>39.65</v>
@@ -5923,27 +5871,27 @@
         <v>-0.216667</v>
       </c>
       <c r="J130" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K130" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M130" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="O130" t="s">
-        <v>20</v>
-      </c>
-      <c r="P130" s="3" t="s">
-        <v>41</v>
+        <v>21</v>
+      </c>
+      <c r="P130" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="131" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B131" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="C131" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
       <c r="D131">
         <v>43.733333000000002</v>
@@ -5952,27 +5900,27 @@
         <v>15.883333</v>
       </c>
       <c r="J131" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K131" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M131" t="s">
-        <v>188</v>
+        <v>189</v>
       </c>
       <c r="O131" t="s">
-        <v>20</v>
-      </c>
-      <c r="P131" s="3" t="s">
-        <v>41</v>
+        <v>21</v>
+      </c>
+      <c r="P131" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="132" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B132" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="C132" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D132">
         <v>40.466667000000001</v>
@@ -5981,27 +5929,27 @@
         <v>17.2</v>
       </c>
       <c r="J132" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K132" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="M132" t="s">
-        <v>189</v>
+        <v>190</v>
       </c>
       <c r="O132" t="s">
-        <v>20</v>
-      </c>
-      <c r="P132" s="3" t="s">
-        <v>41</v>
+        <v>21</v>
+      </c>
+      <c r="P132" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="133" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B133" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="C133" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="D133">
         <v>41.1</v>
@@ -6010,24 +5958,24 @@
         <v>1.233333</v>
       </c>
       <c r="J133" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K133" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M133" t="s">
-        <v>190</v>
+        <v>191</v>
       </c>
       <c r="O133" t="s">
-        <v>20</v>
-      </c>
-      <c r="P133" s="3" t="s">
-        <v>41</v>
+        <v>21</v>
+      </c>
+      <c r="P133" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="134" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B134" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="D134">
         <v>34.9</v>
@@ -6036,27 +5984,27 @@
         <v>35.866667</v>
       </c>
       <c r="J134" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K134" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M134" t="s">
-        <v>191</v>
+        <v>192</v>
       </c>
       <c r="O134" t="s">
-        <v>20</v>
-      </c>
-      <c r="P134" s="3" t="s">
-        <v>41</v>
+        <v>21</v>
+      </c>
+      <c r="P134" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="135" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B135" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="C135" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D135">
         <v>36.316667000000002</v>
@@ -6065,27 +6013,27 @@
         <v>33.883333</v>
       </c>
       <c r="J135" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K135" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M135" t="s">
-        <v>192</v>
+        <v>193</v>
       </c>
       <c r="O135" t="s">
-        <v>20</v>
-      </c>
-      <c r="P135" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="136" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>21</v>
+      </c>
+      <c r="P135" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="136" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B136" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="C136" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D136">
         <v>40.633333</v>
@@ -6094,27 +6042,27 @@
         <v>22.933333000000001</v>
       </c>
       <c r="J136" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K136" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M136" t="s">
-        <v>193</v>
+        <v>194</v>
       </c>
       <c r="O136" t="s">
-        <v>20</v>
-      </c>
-      <c r="P136" s="3" t="s">
-        <v>20</v>
-      </c>
-    </row>
-    <row r="137" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>21</v>
+      </c>
+      <c r="P136" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="137" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B137" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="C137" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D137">
         <v>38.335569999999997</v>
@@ -6123,27 +6071,27 @@
         <v>21.84543</v>
       </c>
       <c r="J137" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K137" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M137" t="s">
-        <v>117</v>
+        <v>118</v>
       </c>
       <c r="O137" t="s">
-        <v>20</v>
-      </c>
-      <c r="P137" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="P137" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="138" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B138" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="C138" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="D138">
         <v>43.1</v>
@@ -6152,27 +6100,27 @@
         <v>5.9166670000000003</v>
       </c>
       <c r="J138" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K138" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M138" t="s">
-        <v>194</v>
+        <v>195</v>
       </c>
       <c r="O138" t="s">
-        <v>20</v>
-      </c>
-      <c r="P138" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="139" spans="2:16" x14ac:dyDescent="0.35">
+        <v>21</v>
+      </c>
+      <c r="P138" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="139" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B139" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="C139" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="D139">
         <v>45.611255</v>
@@ -6181,27 +6129,27 @@
         <v>13.802586</v>
       </c>
       <c r="J139" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K139" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M139" t="s">
-        <v>195</v>
+        <v>196</v>
       </c>
       <c r="O139" t="s">
-        <v>20</v>
-      </c>
-      <c r="P139" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="P139" t="s">
+        <v>21</v>
       </c>
     </row>
     <row r="140" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B140" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="C140" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="D140">
         <v>34.721699999999998</v>
@@ -6210,27 +6158,27 @@
         <v>33.316400000000002</v>
       </c>
       <c r="J140" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K140" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M140" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
       <c r="O140" t="s">
-        <v>20</v>
-      </c>
-      <c r="P140" s="3" t="s">
-        <v>41</v>
+        <v>21</v>
+      </c>
+      <c r="P140" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="141" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B141" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="C141" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D141">
         <v>31.349048100000001</v>
@@ -6239,27 +6187,27 @@
         <v>30.318646600000001</v>
       </c>
       <c r="J141" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K141" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
       <c r="M141" t="s">
-        <v>196</v>
+        <v>197</v>
       </c>
       <c r="O141" t="s">
-        <v>20</v>
-      </c>
-      <c r="P141" s="3" t="s">
-        <v>41</v>
+        <v>21</v>
+      </c>
+      <c r="P141" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="142" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B142" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="C142" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D142">
         <v>32.336415289999998</v>
@@ -6268,27 +6216,27 @@
         <v>15.219913979999999</v>
       </c>
       <c r="J142" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K142" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="M142" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
       <c r="O142" t="s">
-        <v>20</v>
-      </c>
-      <c r="P142" s="3" t="s">
-        <v>41</v>
+        <v>21</v>
+      </c>
+      <c r="P142" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="143" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B143" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="C143" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="D143">
         <v>34.33510777</v>
@@ -6297,27 +6245,27 @@
         <v>35.731147280000002</v>
       </c>
       <c r="J143" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K143" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M143" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="O143" t="s">
-        <v>20</v>
-      </c>
-      <c r="P143" s="3" t="s">
-        <v>41</v>
+        <v>21</v>
+      </c>
+      <c r="P143" t="s">
+        <v>22</v>
       </c>
     </row>
     <row r="144" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
       <c r="B144" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="C144" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="D144">
         <v>39.879589000000003</v>
@@ -6326,27 +6274,27 @@
         <v>26.156554</v>
       </c>
       <c r="J144" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K144" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="M144" t="s">
-        <v>197</v>
+        <v>198</v>
       </c>
       <c r="O144" t="s">
-        <v>20</v>
-      </c>
-      <c r="P144" s="3" t="s">
-        <v>41</v>
-      </c>
-    </row>
-    <row r="145" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>21</v>
+      </c>
+      <c r="P144" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="145" spans="2:16" x14ac:dyDescent="0.35">
       <c r="B145" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="C145" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="D145">
         <v>37.96</v>
@@ -6355,42 +6303,29 @@
         <v>23.4023</v>
       </c>
       <c r="J145" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="K145" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="M145" t="s">
-        <v>198</v>
+        <v>199</v>
       </c>
       <c r="O145" t="s">
-        <v>20</v>
-      </c>
-      <c r="P145" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
+      </c>
+      <c r="P145" t="s">
+        <v>22</v>
       </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:P145" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="1">
+    <filterColumn colId="2">
       <filters>
-        <filter val="Trieste"/>
-      </filters>
-    </filterColumn>
-    <filterColumn colId="15">
-      <filters>
-        <filter val="Yes"/>
+        <filter val="GR"/>
       </filters>
     </filterColumn>
   </autoFilter>
-  <conditionalFormatting sqref="P1:P1048576">
-    <cfRule type="containsText" dxfId="1" priority="1" operator="containsText" text="Yes">
-      <formula>NOT(ISERROR(SEARCH("Yes",P1)))</formula>
-    </cfRule>
-    <cfRule type="containsText" dxfId="0" priority="2" operator="containsText" text="No">
-      <formula>NOT(ISERROR(SEARCH("No",P1)))</formula>
-    </cfRule>
-  </conditionalFormatting>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/2026_project/2_data_processed/intermediate_output/combined_selected_manual_edit.xlsx
+++ b/2026_project/2_data_processed/intermediate_output/combined_selected_manual_edit.xlsx
@@ -1,29 +1,26 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dutka\MT\AdOpT-NET0_dw\2026_project\2_data_processed\intermediate_output\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{215FC4D1-FB24-4F0F-A277-58BDE8E06228}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{13D41ECA-D079-4A77-B44A-B1A52B5493CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-270" yWindow="2080" windowWidth="25470" windowHeight="9220" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$P$145</definedName>
-  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1118" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1264" uniqueCount="202">
   <si>
     <t>group</t>
   </si>
@@ -71,6 +68,12 @@
   </si>
   <si>
     <t>selection</t>
+  </si>
+  <si>
+    <t>selection_2</t>
+  </si>
+  <si>
+    <t>capacity_T_2</t>
   </si>
   <si>
     <t>ACCIAI SPECIALI TERNI S.P.A. - stabilimento di TERNI</t>
@@ -641,6 +644,7 @@
       <b/>
       <sz val="11"/>
       <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="2">
@@ -985,19 +989,10 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <sheetPr filterMode="1"/>
-  <dimension ref="A1:P145"/>
+  <dimension ref="A1:R145"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
-  <cols>
-    <col min="4" max="4" width="11.81640625" customWidth="1"/>
-    <col min="5" max="5" width="21.36328125" customWidth="1"/>
-    <col min="13" max="13" width="24.90625" customWidth="1"/>
-    <col min="14" max="14" width="22" customWidth="1"/>
-    <col min="15" max="15" width="16.453125" customWidth="1"/>
-    <col min="16" max="16" width="26.6328125" customWidth="1"/>
-  </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1046,13 +1041,19 @@
       <c r="P1" s="1" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="2" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+      <c r="Q1" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" s="1" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="2" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="C2" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D2">
         <v>42.566699999999997</v>
@@ -1064,36 +1065,39 @@
         <v>305433.09999999998</v>
       </c>
       <c r="H2" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I2" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J2" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L2">
         <v>2023</v>
       </c>
       <c r="M2" t="s">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="N2">
         <v>34.866792237442922</v>
       </c>
       <c r="O2" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P2" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="Q2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="3" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="C3" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D3">
         <v>46.006700000000002</v>
@@ -1105,36 +1109,39 @@
         <v>259007</v>
       </c>
       <c r="H3" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I3" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J3" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L3">
         <v>2023</v>
       </c>
       <c r="M3" t="s">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="N3">
         <v>29.56700913242009</v>
       </c>
       <c r="O3" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P3" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="Q3" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="4" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="C4" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D4">
         <v>32.423500557796601</v>
@@ -1146,36 +1153,39 @@
         <v>967827.94824338704</v>
       </c>
       <c r="H4" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I4" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J4" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L4">
         <v>2025</v>
       </c>
       <c r="M4" t="s">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="N4">
         <v>110.4826424935373</v>
       </c>
       <c r="O4" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="5" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="C5" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D5">
         <v>43.465510000000002</v>
@@ -1187,36 +1197,39 @@
         <v>3732999.9360000002</v>
       </c>
       <c r="H5" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I5" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J5" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L5">
         <v>2024</v>
       </c>
       <c r="M5" t="s">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="N5">
         <v>426.14154520547947</v>
       </c>
       <c r="O5" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P5" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="6" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B6" t="s">
-        <v>30</v>
+        <v>32</v>
       </c>
       <c r="C6" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D6">
         <v>45.1494</v>
@@ -1228,36 +1241,39 @@
         <v>378667</v>
       </c>
       <c r="H6" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I6" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J6" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L6">
         <v>2023</v>
       </c>
       <c r="M6" t="s">
-        <v>31</v>
+        <v>33</v>
       </c>
       <c r="N6">
         <v>43.226826484018268</v>
       </c>
       <c r="O6" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P6" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="7" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="7" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="C7" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D7">
         <v>36.868661270599297</v>
@@ -1269,36 +1285,39 @@
         <v>984166.4892579451</v>
       </c>
       <c r="H7" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I7" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J7" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L7">
         <v>2025</v>
       </c>
       <c r="M7" t="s">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="N7">
         <v>112.34777274634079</v>
       </c>
       <c r="O7" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P7" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="8" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="8" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="C8" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D8">
         <v>32.520679750585899</v>
@@ -1310,36 +1329,39 @@
         <v>474779.82716398779</v>
       </c>
       <c r="H8" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I8" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J8" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L8">
         <v>2025</v>
       </c>
       <c r="M8" t="s">
-        <v>34</v>
+        <v>36</v>
       </c>
       <c r="N8">
         <v>54.198610406847919</v>
       </c>
       <c r="O8" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P8" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="9" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B9" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C9" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D9">
         <v>34.335107767925798</v>
@@ -1351,36 +1373,39 @@
         <v>1508547.8450828581</v>
       </c>
       <c r="H9" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I9" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J9" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L9">
         <v>2025</v>
       </c>
       <c r="M9" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="N9">
         <v>172.20865811448149</v>
       </c>
       <c r="O9" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P9" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="10" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="10" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B10" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="C10" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D10">
         <v>31.119723669408199</v>
@@ -1392,36 +1417,39 @@
         <v>1493091.3958554219</v>
       </c>
       <c r="H10" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I10" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J10" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L10">
         <v>2025</v>
       </c>
       <c r="M10" t="s">
-        <v>37</v>
+        <v>39</v>
       </c>
       <c r="N10">
         <v>170.44422327116689</v>
       </c>
       <c r="O10" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P10" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="11" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="11" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B11" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="C11" t="s">
-        <v>40</v>
+        <v>42</v>
       </c>
       <c r="D11">
         <v>46.068649999999998</v>
@@ -1433,36 +1461,39 @@
         <v>684374</v>
       </c>
       <c r="H11" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I11" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J11" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L11">
         <v>2024</v>
       </c>
       <c r="M11" t="s">
-        <v>39</v>
+        <v>41</v>
       </c>
       <c r="N11">
         <v>78.12488584474886</v>
       </c>
       <c r="O11" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P11" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="12" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="12" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B12" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="C12" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D12">
         <v>44.7667</v>
@@ -1474,36 +1505,39 @@
         <v>488155.33600000001</v>
       </c>
       <c r="H12" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I12" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J12" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L12">
         <v>2023</v>
       </c>
       <c r="M12" t="s">
-        <v>42</v>
+        <v>44</v>
       </c>
       <c r="N12">
         <v>55.72549497716895</v>
       </c>
       <c r="O12" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="P12" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="13" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B13" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="C13" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D13">
         <v>44.283299999999997</v>
@@ -1515,36 +1549,39 @@
         <v>700973.36</v>
       </c>
       <c r="H13" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I13" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J13" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L13">
         <v>2023</v>
       </c>
       <c r="M13" t="s">
-        <v>43</v>
+        <v>45</v>
       </c>
       <c r="N13">
         <v>80.019789954337895</v>
       </c>
       <c r="O13" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="P13" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="14" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="14" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B14" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="C14" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D14">
         <v>45.254199999999997</v>
@@ -1556,36 +1593,39 @@
         <v>349657.24900000001</v>
       </c>
       <c r="H14" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I14" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J14" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L14">
         <v>2023</v>
       </c>
       <c r="M14" t="s">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="N14">
         <v>39.915211073059361</v>
       </c>
       <c r="O14" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="P14" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="15" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B15" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="C15" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D15">
         <v>38.4563347262105</v>
@@ -1597,36 +1637,39 @@
         <v>493234.8586345205</v>
       </c>
       <c r="H15" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I15" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J15" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L15">
         <v>2025</v>
       </c>
       <c r="M15" t="s">
-        <v>45</v>
+        <v>47</v>
       </c>
       <c r="N15">
         <v>56.305349159191827</v>
       </c>
       <c r="O15" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P15" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="16" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="16" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B16" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="C16" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D16">
         <v>32.005901759509598</v>
@@ -1638,36 +1681,39 @@
         <v>654454.01281724276</v>
       </c>
       <c r="H16" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I16" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J16" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L16">
         <v>2025</v>
       </c>
       <c r="M16" t="s">
-        <v>46</v>
+        <v>48</v>
       </c>
       <c r="N16">
         <v>74.709362193749172</v>
       </c>
       <c r="O16" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P16" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="17" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="17" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B17" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="C17" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D17">
         <v>30.880353032662399</v>
@@ -1679,36 +1725,39 @@
         <v>2366107.1811744389</v>
       </c>
       <c r="H17" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I17" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J17" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L17">
         <v>2025</v>
       </c>
       <c r="M17" t="s">
-        <v>47</v>
+        <v>49</v>
       </c>
       <c r="N17">
         <v>270.10355949479901</v>
       </c>
       <c r="O17" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P17" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="18" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="18" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B18" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="C18" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D18">
         <v>41.5488546799657</v>
@@ -1720,36 +1769,39 @@
         <v>520149.38131691993</v>
       </c>
       <c r="H18" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I18" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J18" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L18">
         <v>2025</v>
       </c>
       <c r="M18" t="s">
-        <v>48</v>
+        <v>50</v>
       </c>
       <c r="N18">
         <v>59.37778325535615</v>
       </c>
       <c r="O18" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P18" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="19" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="19" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B19" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="C19" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D19">
         <v>37.194443999999997</v>
@@ -1761,36 +1813,39 @@
         <v>395619.44099999999</v>
       </c>
       <c r="H19" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I19" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J19" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L19">
         <v>2023</v>
       </c>
       <c r="M19" t="s">
-        <v>50</v>
+        <v>52</v>
       </c>
       <c r="N19">
         <v>45.162036643835613</v>
       </c>
       <c r="O19" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P19" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="20" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="20" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B20" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="C20" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D20">
         <v>41.316699999999997</v>
@@ -1802,36 +1857,39 @@
         <v>326744.86</v>
       </c>
       <c r="H20" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I20" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J20" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L20">
         <v>2023</v>
       </c>
       <c r="M20" t="s">
-        <v>51</v>
+        <v>53</v>
       </c>
       <c r="N20">
         <v>37.299641552511417</v>
       </c>
       <c r="O20" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P20" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="21" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="21" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B21" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="C21" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D21">
         <v>42.000100000000003</v>
@@ -1843,36 +1901,39 @@
         <v>383770.34899999999</v>
       </c>
       <c r="H21" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I21" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J21" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L21">
         <v>2023</v>
       </c>
       <c r="M21" t="s">
-        <v>52</v>
+        <v>54</v>
       </c>
       <c r="N21">
         <v>43.809400570776248</v>
       </c>
       <c r="O21" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P21" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="22" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="22" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B22" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="C22" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D22">
         <v>45.877777000000002</v>
@@ -1884,36 +1945,39 @@
         <v>332973</v>
       </c>
       <c r="H22" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I22" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J22" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L22">
         <v>2023</v>
       </c>
       <c r="M22" t="s">
-        <v>53</v>
+        <v>55</v>
       </c>
       <c r="N22">
         <v>38.010616438356173</v>
       </c>
       <c r="O22" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="P22" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="23" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="23" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B23" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="C23" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D23">
         <v>41.408723000000002</v>
@@ -1925,36 +1989,39 @@
         <v>905000</v>
       </c>
       <c r="H23" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I23" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J23" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L23">
         <v>2024</v>
       </c>
       <c r="M23" t="s">
-        <v>54</v>
+        <v>56</v>
       </c>
       <c r="N23">
         <v>103.310502283105</v>
       </c>
       <c r="O23" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P23" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="24" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="24" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B24" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C24" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D24">
         <v>41.314664999999998</v>
@@ -1966,36 +2033,39 @@
         <v>928000</v>
       </c>
       <c r="H24" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I24" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J24" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L24">
         <v>2024</v>
       </c>
       <c r="M24" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="N24">
         <v>105.93607305936069</v>
       </c>
       <c r="O24" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P24" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="25" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="25" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B25" t="s">
+        <v>59</v>
+      </c>
+      <c r="C25" t="s">
         <v>57</v>
-      </c>
-      <c r="C25" t="s">
-        <v>55</v>
       </c>
       <c r="D25">
         <v>40.578910999999998</v>
@@ -2007,36 +2077,39 @@
         <v>592000</v>
       </c>
       <c r="H25" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I25" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J25" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L25">
         <v>2024</v>
       </c>
       <c r="M25" t="s">
-        <v>57</v>
+        <v>59</v>
       </c>
       <c r="N25">
         <v>67.579908675799089</v>
       </c>
       <c r="O25" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P25" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="26" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="26" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B26" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="C26" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D26">
         <v>38.378608</v>
@@ -2048,36 +2121,39 @@
         <v>584000</v>
       </c>
       <c r="H26" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I26" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J26" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L26">
         <v>2024</v>
       </c>
       <c r="M26" t="s">
-        <v>58</v>
+        <v>60</v>
       </c>
       <c r="N26">
         <v>66.666666666666671</v>
       </c>
       <c r="O26" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P26" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="27" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="27" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B27" t="s">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="C27" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D27">
         <v>41.445599999999999</v>
@@ -2089,36 +2165,39 @@
         <v>689345</v>
       </c>
       <c r="H27" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I27" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J27" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L27">
         <v>2023</v>
       </c>
       <c r="M27" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="N27">
         <v>78.692351598173516</v>
       </c>
       <c r="O27" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P27" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="28" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="28" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B28" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="C28" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D28">
         <v>43.284399999999998</v>
@@ -2130,36 +2209,39 @@
         <v>336074</v>
       </c>
       <c r="H28" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I28" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J28" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L28">
         <v>2023</v>
       </c>
       <c r="M28" t="s">
-        <v>61</v>
+        <v>63</v>
       </c>
       <c r="N28">
         <v>38.364611872146121</v>
       </c>
       <c r="O28" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P28" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="29" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="29" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B29" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="C29" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D29">
         <v>43.658099999999997</v>
@@ -2171,36 +2253,39 @@
         <v>402310</v>
       </c>
       <c r="H29" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I29" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J29" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L29">
         <v>2023</v>
       </c>
       <c r="M29" t="s">
-        <v>62</v>
+        <v>64</v>
       </c>
       <c r="N29">
         <v>45.925799086757991</v>
       </c>
       <c r="O29" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P29" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="30" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="30" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B30" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="C30" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D30">
         <v>40.9497</v>
@@ -2212,36 +2297,39 @@
         <v>246153.96</v>
       </c>
       <c r="H30" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I30" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J30" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L30">
         <v>2023</v>
       </c>
       <c r="M30" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="N30">
         <v>28.09976712328767</v>
       </c>
       <c r="O30" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P30" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="31" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="31" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B31" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C31" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D31">
         <v>46.177799999999998</v>
@@ -2253,36 +2341,39 @@
         <v>423066.01</v>
       </c>
       <c r="H31" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I31" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J31" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L31">
         <v>2023</v>
       </c>
       <c r="M31" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="N31">
         <v>48.295206621004567</v>
       </c>
       <c r="O31" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="P31" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="32" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="32" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B32" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="C32" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D32">
         <v>38.4266767746672</v>
@@ -2294,36 +2385,39 @@
         <v>637071.14593878668</v>
       </c>
       <c r="H32" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I32" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J32" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L32">
         <v>2025</v>
       </c>
       <c r="M32" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="N32">
         <v>72.725016659678843</v>
       </c>
       <c r="O32" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P32" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="33" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="33" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B33" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="C33" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D33">
         <v>31.141703251211499</v>
@@ -2335,36 +2429,39 @@
         <v>445040.90318066528</v>
       </c>
       <c r="H33" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I33" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J33" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L33">
         <v>2025</v>
       </c>
       <c r="M33" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="N33">
         <v>50.803756070852209</v>
       </c>
       <c r="O33" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P33" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="34" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="34" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B34" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="C34" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D34">
         <v>43.420110000000001</v>
@@ -2376,36 +2473,39 @@
         <v>312000</v>
       </c>
       <c r="H34" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I34" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J34" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L34">
         <v>2024</v>
       </c>
       <c r="M34" t="s">
-        <v>67</v>
+        <v>69</v>
       </c>
       <c r="N34">
         <v>35.61643835616438</v>
       </c>
       <c r="O34" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P34" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="35" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="35" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B35" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="C35" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D35">
         <v>38.727834458232799</v>
@@ -2417,36 +2517,39 @@
         <v>257755.10755995769</v>
       </c>
       <c r="H35" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I35" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J35" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L35">
         <v>2025</v>
       </c>
       <c r="M35" t="s">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="N35">
         <v>29.424099036524861</v>
       </c>
       <c r="O35" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P35" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="36" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="Q35" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="36" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B36" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="C36" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D36">
         <v>36.690885291978802</v>
@@ -2458,36 +2561,39 @@
         <v>201371.17778121689</v>
       </c>
       <c r="H36" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I36" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J36" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L36">
         <v>2025</v>
       </c>
       <c r="M36" t="s">
-        <v>70</v>
+        <v>72</v>
       </c>
       <c r="N36">
         <v>22.987577372285038</v>
       </c>
       <c r="O36" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P36" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="37" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="37" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B37" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="C37" t="s">
-        <v>72</v>
+        <v>74</v>
       </c>
       <c r="D37">
         <v>34.972277654515203</v>
@@ -2499,36 +2605,39 @@
         <v>599688.7049220067</v>
       </c>
       <c r="H37" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I37" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J37" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L37">
         <v>2025</v>
       </c>
       <c r="M37" t="s">
-        <v>71</v>
+        <v>73</v>
       </c>
       <c r="N37">
         <v>68.457614717124059</v>
       </c>
       <c r="O37" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P37" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="38" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="Q37" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="38" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B38" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="C38" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D38">
         <v>39.8638011379185</v>
@@ -2540,36 +2649,39 @@
         <v>1773286.7549579451</v>
       </c>
       <c r="H38" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I38" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J38" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L38">
         <v>2025</v>
       </c>
       <c r="M38" t="s">
-        <v>73</v>
+        <v>75</v>
       </c>
       <c r="N38">
         <v>202.42999485821289</v>
       </c>
       <c r="O38" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P38" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="39" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="39" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B39" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="C39" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D39">
         <v>41.503774444497097</v>
@@ -2581,36 +2693,39 @@
         <v>432440.56989697582</v>
       </c>
       <c r="H39" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I39" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J39" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L39">
         <v>2025</v>
       </c>
       <c r="M39" t="s">
-        <v>74</v>
+        <v>76</v>
       </c>
       <c r="N39">
         <v>49.365361860385363</v>
       </c>
       <c r="O39" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P39" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="40" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="40" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B40" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C40" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D40">
         <v>36.966500000000003</v>
@@ -2622,36 +2737,39 @@
         <v>749000</v>
       </c>
       <c r="H40" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I40" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J40" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L40">
         <v>2024</v>
       </c>
       <c r="M40" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="N40">
         <v>85.502283105022826</v>
       </c>
       <c r="O40" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P40" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="41" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="41" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B41" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="C41" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D41">
         <v>36.716600999999997</v>
@@ -2663,36 +2781,39 @@
         <v>613000</v>
       </c>
       <c r="H41" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I41" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J41" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L41">
         <v>2024</v>
       </c>
       <c r="M41" t="s">
-        <v>76</v>
+        <v>78</v>
       </c>
       <c r="N41">
         <v>69.977168949771695</v>
       </c>
       <c r="O41" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P41" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="42" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="Q41" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="42" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B42" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="C42" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D42">
         <v>41.477659000000003</v>
@@ -2704,36 +2825,39 @@
         <v>424000</v>
       </c>
       <c r="H42" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I42" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J42" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L42">
         <v>2024</v>
       </c>
       <c r="M42" t="s">
-        <v>77</v>
+        <v>79</v>
       </c>
       <c r="N42">
         <v>48.401826484018272</v>
       </c>
       <c r="O42" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P42" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="43" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="Q42" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="43" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B43" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="C43" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D43">
         <v>43.792389999999997</v>
@@ -2745,36 +2869,39 @@
         <v>391000</v>
       </c>
       <c r="H43" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I43" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J43" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L43">
         <v>2024</v>
       </c>
       <c r="M43" t="s">
-        <v>78</v>
+        <v>80</v>
       </c>
       <c r="N43">
         <v>44.634703196347033</v>
       </c>
       <c r="O43" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P43" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="44" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="Q43" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="44" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B44" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C44" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D44">
         <v>45.684699999999999</v>
@@ -2786,36 +2913,39 @@
         <v>722839</v>
       </c>
       <c r="H44" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I44" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J44" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L44">
         <v>2023</v>
       </c>
       <c r="M44" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="N44">
         <v>82.515867579908672</v>
       </c>
       <c r="O44" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="P44" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="45" spans="2:16" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+      <c r="Q44" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="45" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B45" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C45" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D45">
         <v>39.351709999999997</v>
@@ -2827,36 +2957,39 @@
         <v>1031000</v>
       </c>
       <c r="H45" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I45" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J45" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L45">
         <v>2024</v>
       </c>
       <c r="M45" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="N45">
         <v>117.6940639269406</v>
       </c>
       <c r="O45" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P45" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="46" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="Q45" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="46" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B46" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="C46" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D46">
         <v>44.671399999999998</v>
@@ -2868,36 +3001,39 @@
         <v>221172.83040000001</v>
       </c>
       <c r="H46" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I46" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J46" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L46">
         <v>2023</v>
       </c>
       <c r="M46" t="s">
-        <v>82</v>
+        <v>84</v>
       </c>
       <c r="N46">
         <v>25.24804</v>
       </c>
       <c r="O46" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="P46" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="47" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+      <c r="Q46" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="47" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B47" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C47" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D47">
         <v>45.6111</v>
@@ -2909,36 +3045,39 @@
         <v>207266.76</v>
       </c>
       <c r="H47" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I47" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J47" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L47">
         <v>2023</v>
       </c>
       <c r="M47" t="s">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="N47">
         <v>23.660589041095889</v>
       </c>
       <c r="O47" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="P47" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="48" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+      <c r="Q47" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="48" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B48" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C48" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D48">
         <v>45.515300000000003</v>
@@ -2950,36 +3089,39 @@
         <v>808186</v>
       </c>
       <c r="H48" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I48" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J48" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L48">
         <v>2023</v>
       </c>
       <c r="M48" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="N48">
         <v>92.25867579908676</v>
       </c>
       <c r="O48" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="P48" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="49" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+      <c r="Q48" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="49" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B49" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="C49" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D49">
         <v>39.666317999999997</v>
@@ -2991,36 +3133,39 @@
         <v>648000</v>
       </c>
       <c r="H49" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I49" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J49" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L49">
         <v>2024</v>
       </c>
       <c r="M49" t="s">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="N49">
         <v>73.972602739726028</v>
       </c>
       <c r="O49" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P49" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="50" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="Q49" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="50" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B50" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C50" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D50">
         <v>38.750794080123498</v>
@@ -3032,36 +3177,39 @@
         <v>264345.06915039301</v>
       </c>
       <c r="H50" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I50" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J50" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L50">
         <v>2025</v>
       </c>
       <c r="M50" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="N50">
         <v>30.17637775689418</v>
       </c>
       <c r="O50" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P50" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="51" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="Q50" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="51" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B51" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="C51" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D51">
         <v>41.736699999999999</v>
@@ -3073,36 +3221,39 @@
         <v>326434</v>
       </c>
       <c r="H51" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I51" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J51" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L51">
         <v>2023</v>
       </c>
       <c r="M51" t="s">
-        <v>88</v>
+        <v>90</v>
       </c>
       <c r="N51">
         <v>37.264155251141553</v>
       </c>
       <c r="O51" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P51" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="52" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="Q51" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="52" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B52" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C52" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D52">
         <v>34.306566324113</v>
@@ -3114,36 +3265,39 @@
         <v>1037263.135995616</v>
       </c>
       <c r="H52" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I52" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J52" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L52">
         <v>2025</v>
       </c>
       <c r="M52" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="N52">
         <v>118.4090337894539</v>
       </c>
       <c r="O52" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P52" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="53" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="Q52" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="53" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B53" t="s">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="C53" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D53">
         <v>45.049700000000001</v>
@@ -3155,36 +3309,39 @@
         <v>330208</v>
       </c>
       <c r="H53" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I53" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J53" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L53">
         <v>2023</v>
       </c>
       <c r="M53" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="N53">
         <v>37.694977168949769</v>
       </c>
       <c r="O53" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="P53" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="54" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+      <c r="Q53" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="54" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B54" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="C54" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D54">
         <v>45.408299999999997</v>
@@ -3196,36 +3353,39 @@
         <v>206634.7028</v>
       </c>
       <c r="H54" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I54" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J54" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L54">
         <v>2023</v>
       </c>
       <c r="M54" t="s">
-        <v>92</v>
+        <v>94</v>
       </c>
       <c r="N54">
         <v>23.58843639269406</v>
       </c>
       <c r="O54" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="P54" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="55" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+      <c r="Q54" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="55" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B55" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="C55" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D55">
         <v>45.504199999999997</v>
@@ -3237,36 +3397,39 @@
         <v>277838.32900000003</v>
       </c>
       <c r="H55" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I55" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J55" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L55">
         <v>2023</v>
       </c>
       <c r="M55" t="s">
-        <v>93</v>
+        <v>95</v>
       </c>
       <c r="N55">
         <v>31.716704223744291</v>
       </c>
       <c r="O55" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="P55" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="56" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+      <c r="Q55" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="56" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B56" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C56" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D56">
         <v>36.735732350892</v>
@@ -3278,36 +3441,39 @@
         <v>6477157.1833037036</v>
       </c>
       <c r="H56" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I56" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J56" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L56">
         <v>2025</v>
       </c>
       <c r="M56" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="N56">
         <v>739.40150494334512</v>
       </c>
       <c r="O56" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P56" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="57" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="Q56" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="57" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B57" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C57" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D57">
         <v>40.6753</v>
@@ -3319,36 +3485,39 @@
         <v>390621</v>
       </c>
       <c r="H57" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I57" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J57" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L57">
         <v>2023</v>
       </c>
       <c r="M57" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="N57">
         <v>44.591438356164382</v>
       </c>
       <c r="O57" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P57" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="58" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="Q57" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="58" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B58" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="C58" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D58">
         <v>38.190832999999998</v>
@@ -3360,36 +3529,39 @@
         <v>263673</v>
       </c>
       <c r="H58" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I58" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J58" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L58">
         <v>2023</v>
       </c>
       <c r="M58" t="s">
-        <v>96</v>
+        <v>98</v>
       </c>
       <c r="N58">
         <v>30.099657534246571</v>
       </c>
       <c r="O58" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P58" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="59" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="Q58" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="59" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B59" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="C59" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D59">
         <v>38.742497000573699</v>
@@ -3401,36 +3573,39 @@
         <v>201371.17778121689</v>
       </c>
       <c r="H59" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I59" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J59" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L59">
         <v>2025</v>
       </c>
       <c r="M59" t="s">
-        <v>97</v>
+        <v>99</v>
       </c>
       <c r="N59">
         <v>22.987577372285038</v>
       </c>
       <c r="O59" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P59" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="60" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="Q59" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="60" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B60" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="C60" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D60">
         <v>43.022080000000003</v>
@@ -3442,36 +3617,39 @@
         <v>454000</v>
       </c>
       <c r="H60" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I60" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J60" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L60">
         <v>2024</v>
       </c>
       <c r="M60" t="s">
-        <v>98</v>
+        <v>100</v>
       </c>
       <c r="N60">
         <v>51.826484018264843</v>
       </c>
       <c r="O60" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P60" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="61" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="Q60" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="61" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B61" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C61" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D61">
         <v>45.2804</v>
@@ -3483,36 +3661,39 @@
         <v>254107</v>
       </c>
       <c r="H61" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I61" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J61" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L61">
         <v>2023</v>
       </c>
       <c r="M61" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="N61">
         <v>29.007648401826479</v>
       </c>
       <c r="O61" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="P61" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="62" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+      <c r="Q61" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="62" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B62" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C62" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D62">
         <v>32.336415294557497</v>
@@ -3524,36 +3705,39 @@
         <v>1031558</v>
       </c>
       <c r="H62" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I62" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J62" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L62">
         <v>2025</v>
       </c>
       <c r="M62" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="N62">
         <v>117.7577625570776</v>
       </c>
       <c r="O62" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P62" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="63" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="Q62" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="63" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B63" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="C63" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D63">
         <v>36.781410300080097</v>
@@ -3565,36 +3749,39 @@
         <v>727575.77467714867</v>
       </c>
       <c r="H63" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I63" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J63" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L63">
         <v>2025</v>
       </c>
       <c r="M63" t="s">
-        <v>101</v>
+        <v>103</v>
       </c>
       <c r="N63">
         <v>83.056595282779526</v>
       </c>
       <c r="O63" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P63" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="64" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="Q63" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="64" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B64" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="C64" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D64">
         <v>32.6169677543662</v>
@@ -3606,36 +3793,39 @@
         <v>260534.99053302259</v>
       </c>
       <c r="H64" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I64" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J64" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L64">
         <v>2025</v>
       </c>
       <c r="M64" t="s">
-        <v>102</v>
+        <v>104</v>
       </c>
       <c r="N64">
         <v>29.741437275459202</v>
       </c>
       <c r="O64" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P64" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="65" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="Q64" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="65" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B65" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="C65" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D65">
         <v>41.419170999999999</v>
@@ -3647,36 +3837,39 @@
         <v>323000</v>
       </c>
       <c r="H65" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I65" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J65" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L65">
         <v>2024</v>
       </c>
       <c r="M65" t="s">
-        <v>103</v>
+        <v>105</v>
       </c>
       <c r="N65">
         <v>36.87214611872146</v>
       </c>
       <c r="O65" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P65" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="66" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="Q65" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="66" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B66" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="C66" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D66">
         <v>44.967320000000001</v>
@@ -3688,36 +3881,39 @@
         <v>314000</v>
       </c>
       <c r="H66" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I66" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J66" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L66">
         <v>2024</v>
       </c>
       <c r="M66" t="s">
-        <v>104</v>
+        <v>106</v>
       </c>
       <c r="N66">
         <v>35.844748858447488</v>
       </c>
       <c r="O66" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P66" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="67" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="Q66" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="67" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B67" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="C67" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D67">
         <v>36.903055999999999</v>
@@ -3729,36 +3925,39 @@
         <v>281353</v>
       </c>
       <c r="H67" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I67" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J67" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L67">
         <v>2023</v>
       </c>
       <c r="M67" t="s">
-        <v>106</v>
+        <v>108</v>
       </c>
       <c r="N67">
         <v>32.117922374429227</v>
       </c>
       <c r="O67" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P67" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="68" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="Q67" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="68" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B68" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C68" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D68">
         <v>31.916468054311501</v>
@@ -3770,36 +3969,39 @@
         <v>1155048.4074455709</v>
       </c>
       <c r="H68" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I68" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J68" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L68">
         <v>2025</v>
       </c>
       <c r="M68" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="N68">
         <v>131.85484103259941</v>
       </c>
       <c r="O68" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P68" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="69" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="Q68" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="69" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B69" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C69" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D69">
         <v>40.5167</v>
@@ -3811,36 +4013,39 @@
         <v>4351958.3</v>
       </c>
       <c r="H69" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I69" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J69" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L69">
         <v>2023</v>
       </c>
       <c r="M69" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="N69">
         <v>496.79889269406391</v>
       </c>
       <c r="O69" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P69" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="70" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="Q69" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="70" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B70" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="C70" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D70">
         <v>36.933010275675301</v>
@@ -3852,36 +4057,39 @@
         <v>531302.09106205474</v>
       </c>
       <c r="H70" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I70" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J70" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L70">
         <v>2025</v>
       </c>
       <c r="M70" t="s">
-        <v>110</v>
+        <v>112</v>
       </c>
       <c r="N70">
         <v>60.650923637220863</v>
       </c>
       <c r="O70" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P70" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="71" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="Q70" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="71" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B71" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C71" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D71">
         <v>33.628254108861398</v>
@@ -3893,36 +4101,39 @@
         <v>413849.33665999997</v>
       </c>
       <c r="H71" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I71" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J71" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L71">
         <v>2025</v>
       </c>
       <c r="M71" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="N71">
         <v>47.243074961187212</v>
       </c>
       <c r="O71" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P71" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="72" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="Q71" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="72" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B72" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="C72" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D72">
         <v>36.2630234976574</v>
@@ -3934,36 +4145,39 @@
         <v>2035690.794484779</v>
       </c>
       <c r="H72" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I72" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J72" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L72">
         <v>2025</v>
       </c>
       <c r="M72" t="s">
-        <v>112</v>
+        <v>114</v>
       </c>
       <c r="N72">
         <v>232.38479389095659</v>
       </c>
       <c r="O72" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P72" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="73" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="Q72" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="73" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B73" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C73" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D73">
         <v>43.363599999999998</v>
@@ -3975,36 +4189,39 @@
         <v>482587</v>
       </c>
       <c r="H73" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I73" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J73" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L73">
         <v>2023</v>
       </c>
       <c r="M73" t="s">
-        <v>114</v>
+        <v>116</v>
       </c>
       <c r="N73">
         <v>55.089840182648402</v>
       </c>
       <c r="O73" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P73" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="74" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="Q73" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="74" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B74" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C74" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D74">
         <v>37.770531602188598</v>
@@ -4016,36 +4233,39 @@
         <v>1830468.2922518109</v>
       </c>
       <c r="H74" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I74" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J74" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L74">
         <v>2025</v>
       </c>
       <c r="M74" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="N74">
         <v>208.9575676086543</v>
       </c>
       <c r="O74" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P74" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="75" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="Q74" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="75" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B75" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="C75" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D75">
         <v>40.966700000000003</v>
@@ -4057,36 +4277,39 @@
         <v>393166.2671</v>
       </c>
       <c r="H75" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I75" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J75" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L75">
         <v>2023</v>
       </c>
       <c r="M75" t="s">
-        <v>116</v>
+        <v>118</v>
       </c>
       <c r="N75">
         <v>44.881993961187213</v>
       </c>
       <c r="O75" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P75" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="76" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="Q75" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="76" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B76" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C76" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D76">
         <v>39.644351</v>
@@ -4098,36 +4321,39 @@
         <v>560000</v>
       </c>
       <c r="H76" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I76" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J76" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L76">
         <v>2024</v>
       </c>
       <c r="M76" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="N76">
         <v>63.926940639269397</v>
       </c>
       <c r="O76" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P76" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="77" spans="2:16" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="Q76" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="77" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B77" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C77" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D77">
         <v>38.335569999999997</v>
@@ -4139,36 +4365,39 @@
         <v>552000</v>
       </c>
       <c r="H77" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I77" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J77" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L77">
         <v>2024</v>
       </c>
       <c r="M77" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="N77">
         <v>63.013698630136993</v>
       </c>
       <c r="O77" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="P77" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="78" spans="2:16" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="Q77" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="78" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B78" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C78" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D78">
         <v>38.130180000000003</v>
@@ -4180,36 +4409,39 @@
         <v>1186000</v>
       </c>
       <c r="H78" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I78" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J78" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L78">
         <v>2024</v>
       </c>
       <c r="M78" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="N78">
         <v>135.38812785388129</v>
       </c>
       <c r="O78" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="P78" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="79" spans="2:16" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="Q78" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="79" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B79" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="C79" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D79">
         <v>40.699100000000001</v>
@@ -4221,36 +4453,39 @@
         <v>606000</v>
       </c>
       <c r="H79" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I79" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J79" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L79">
         <v>2024</v>
       </c>
       <c r="M79" t="s">
-        <v>120</v>
+        <v>122</v>
       </c>
       <c r="N79">
         <v>69.178082191780817</v>
       </c>
       <c r="O79" t="s">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="P79" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="80" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="Q79" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="80" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B80" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C80" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D80">
         <v>43.541710000000002</v>
@@ -4262,36 +4497,39 @@
         <v>544000</v>
       </c>
       <c r="H80" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I80" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J80" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L80">
         <v>2024</v>
       </c>
       <c r="M80" t="s">
-        <v>122</v>
+        <v>124</v>
       </c>
       <c r="N80">
         <v>62.100456621004568</v>
       </c>
       <c r="O80" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P80" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="81" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="Q80" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="81" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B81" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C81" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D81">
         <v>45.642499999999998</v>
@@ -4303,36 +4541,39 @@
         <v>402532.05</v>
       </c>
       <c r="H81" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I81" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J81" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L81">
         <v>2023</v>
       </c>
       <c r="M81" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="N81">
         <v>45.95114726027397</v>
       </c>
       <c r="O81" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P81" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="82" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+      <c r="Q81" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="82" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B82" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="C82" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D82">
         <v>45.788600000000002</v>
@@ -4344,36 +4585,39 @@
         <v>231572</v>
       </c>
       <c r="H82" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I82" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J82" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L82">
         <v>2023</v>
       </c>
       <c r="M82" t="s">
-        <v>124</v>
+        <v>126</v>
       </c>
       <c r="N82">
         <v>26.4351598173516</v>
       </c>
       <c r="O82" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P82" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="83" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+      <c r="Q82" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="83" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B83" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C83" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D83">
         <v>45.459400000000002</v>
@@ -4385,36 +4629,39 @@
         <v>203439</v>
       </c>
       <c r="H83" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I83" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J83" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L83">
         <v>2023</v>
       </c>
       <c r="M83" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="N83">
         <v>23.223630136986301</v>
       </c>
       <c r="O83" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P83" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="84" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+      <c r="Q83" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="84" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B84" t="s">
-        <v>126</v>
+        <v>128</v>
       </c>
       <c r="C84" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D84">
         <v>41.4375</v>
@@ -4426,36 +4673,39 @@
         <v>380667</v>
       </c>
       <c r="H84" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I84" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J84" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L84">
         <v>2023</v>
       </c>
       <c r="M84" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="N84">
         <v>43.455136986301369</v>
       </c>
       <c r="O84" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P84" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="85" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="Q84" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="85" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B85" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C85" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D85">
         <v>34.721699999999998</v>
@@ -4467,36 +4717,39 @@
         <v>1370000</v>
       </c>
       <c r="H85" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I85" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J85" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L85">
         <v>2023</v>
       </c>
       <c r="M85" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="N85">
         <v>156.39269406392691</v>
       </c>
       <c r="O85" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P85" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="86" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="Q85" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="86" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B86" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="C86" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D86">
         <v>43.768630000000002</v>
@@ -4508,36 +4761,39 @@
         <v>434000</v>
       </c>
       <c r="H86" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I86" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J86" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L86">
         <v>2024</v>
       </c>
       <c r="M86" t="s">
-        <v>130</v>
+        <v>132</v>
       </c>
       <c r="N86">
         <v>49.543378995433791</v>
       </c>
       <c r="O86" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P86" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="87" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="Q86" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="87" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B87" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C87" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D87">
         <v>36.964332544555901</v>
@@ -4549,36 +4805,39 @@
         <v>2114795.906676</v>
       </c>
       <c r="H87" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="I87" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J87" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L87">
         <v>2025</v>
       </c>
       <c r="M87" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="N87">
         <v>241.41505783972599</v>
       </c>
       <c r="O87" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P87" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="88" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="Q87" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="88" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B88" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="C88" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D88">
         <v>43.136479999999999</v>
@@ -4590,36 +4849,39 @@
         <v>201000</v>
       </c>
       <c r="H88" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="I88" t="s">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="J88" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L88">
         <v>2024</v>
       </c>
       <c r="M88" t="s">
-        <v>132</v>
+        <v>134</v>
       </c>
       <c r="N88">
         <v>22.94520547945206</v>
       </c>
       <c r="O88" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P88" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="89" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="Q88" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="89" spans="1:18" x14ac:dyDescent="0.35">
       <c r="B89" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C89" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D89">
         <v>38.740041692079899</v>
@@ -4631,39 +4893,42 @@
         <v>216156.41968828891</v>
       </c>
       <c r="H89" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="I89" t="s">
-        <v>27</v>
+        <v>29</v>
       </c>
       <c r="J89" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="L89">
         <v>2025</v>
       </c>
       <c r="M89" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="N89">
         <v>24.675390375375439</v>
       </c>
       <c r="O89" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P89" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="90" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="Q89" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="90" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A90" t="s">
-        <v>134</v>
+        <v>136</v>
       </c>
       <c r="B90" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C90" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D90">
         <v>31.9725</v>
@@ -4675,30 +4940,36 @@
         <v>398430000</v>
       </c>
       <c r="I90" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="J90" t="s">
+        <v>139</v>
+      </c>
+      <c r="M90" t="s">
         <v>137</v>
       </c>
-      <c r="M90" t="s">
-        <v>135</v>
-      </c>
       <c r="O90" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P90" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="91" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="Q90" t="s">
+        <v>24</v>
+      </c>
+      <c r="R90">
+        <v>398430000</v>
+      </c>
+    </row>
+    <row r="91" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A91" t="s">
-        <v>138</v>
+        <v>140</v>
       </c>
       <c r="B91" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C91" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D91">
         <v>31.617999999999999</v>
@@ -4710,30 +4981,36 @@
         <v>179110000</v>
       </c>
       <c r="I91" t="s">
-        <v>136</v>
+        <v>138</v>
       </c>
       <c r="J91" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="M91" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="O91" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P91" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="92" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="Q91" t="s">
+        <v>24</v>
+      </c>
+      <c r="R91">
+        <v>179110000</v>
+      </c>
+    </row>
+    <row r="92" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A92" t="s">
-        <v>140</v>
+        <v>142</v>
       </c>
       <c r="B92" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C92" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D92">
         <v>40.716999999999999</v>
@@ -4745,30 +5022,36 @@
         <v>54000000</v>
       </c>
       <c r="I92" t="s">
-        <v>142</v>
+        <v>144</v>
       </c>
       <c r="J92" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="M92" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="O92" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P92" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="93" spans="1:16" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="Q92" t="s">
+        <v>24</v>
+      </c>
+      <c r="R92">
+        <v>54000000</v>
+      </c>
+    </row>
+    <row r="93" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A93" t="s">
-        <v>143</v>
+        <v>145</v>
       </c>
       <c r="B93" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="C93" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D93">
         <v>40.802035296804902</v>
@@ -4780,30 +5063,36 @@
         <v>66400000.000000007</v>
       </c>
       <c r="I93" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="J93" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="M93" t="s">
-        <v>144</v>
+        <v>146</v>
       </c>
       <c r="O93" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P93" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="94" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+      <c r="Q93" t="s">
+        <v>24</v>
+      </c>
+      <c r="R93">
+        <v>27400000</v>
+      </c>
+    </row>
+    <row r="94" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A94" t="s">
-        <v>146</v>
+        <v>148</v>
       </c>
       <c r="B94" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C94" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D94">
         <v>43.601553631123352</v>
@@ -4815,30 +5104,36 @@
         <v>444985000</v>
       </c>
       <c r="I94" t="s">
-        <v>148</v>
+        <v>150</v>
       </c>
       <c r="J94" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="M94" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="O94" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P94" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="95" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="Q94" t="s">
+        <v>24</v>
+      </c>
+      <c r="R94">
+        <v>444985000</v>
+      </c>
+    </row>
+    <row r="95" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A95" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="B95" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="C95" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D95">
         <v>44.387</v>
@@ -4850,30 +5145,36 @@
         <v>515000000</v>
       </c>
       <c r="I95" t="s">
-        <v>145</v>
+        <v>147</v>
       </c>
       <c r="J95" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="M95" t="s">
-        <v>150</v>
+        <v>152</v>
       </c>
       <c r="O95" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P95" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="96" spans="1:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+      <c r="Q95" t="s">
+        <v>24</v>
+      </c>
+      <c r="R95">
+        <v>418875000</v>
+      </c>
+    </row>
+    <row r="96" spans="1:18" x14ac:dyDescent="0.35">
       <c r="A96" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="B96" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="C96" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D96">
         <v>39.114235999999998</v>
@@ -4885,27 +5186,33 @@
         <v>130000000</v>
       </c>
       <c r="I96" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="J96" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="M96" t="s">
-        <v>152</v>
+        <v>154</v>
       </c>
       <c r="O96" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P96" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="97" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="Q96" t="s">
+        <v>24</v>
+      </c>
+      <c r="R96">
+        <v>130000000</v>
+      </c>
+    </row>
+    <row r="97" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B97" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C97" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D97">
         <v>38.333333000000003</v>
@@ -4914,27 +5221,30 @@
         <v>-0.48333300000000001</v>
       </c>
       <c r="J97" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="K97" t="s">
+        <v>158</v>
+      </c>
+      <c r="M97" t="s">
         <v>156</v>
       </c>
-      <c r="M97" t="s">
-        <v>154</v>
-      </c>
       <c r="O97" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P97" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="98" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="Q97" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="98" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B98" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="C98" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D98">
         <v>43.628999999999998</v>
@@ -4943,27 +5253,30 @@
         <v>13.494</v>
       </c>
       <c r="J98" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="K98" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="M98" t="s">
-        <v>157</v>
+        <v>159</v>
       </c>
       <c r="O98" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P98" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="99" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="Q98" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="99" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B99" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="C99" t="s">
-        <v>108</v>
+        <v>110</v>
       </c>
       <c r="D99">
         <v>31.816666999999999</v>
@@ -4972,27 +5285,30 @@
         <v>34.65</v>
       </c>
       <c r="J99" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="K99" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="M99" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="O99" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P99" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="100" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="Q99" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="100" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B100" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="C100" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D100">
         <v>37.216667000000001</v>
@@ -5001,27 +5317,30 @@
         <v>15.233333</v>
       </c>
       <c r="J100" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="K100" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="M100" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="O100" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P100" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="101" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="Q100" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="101" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B101" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="C101" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D101">
         <v>32.116667</v>
@@ -5030,27 +5349,30 @@
         <v>20.05</v>
       </c>
       <c r="J101" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="K101" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="M101" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="O101" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P101" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="102" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="Q101" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="102" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B102" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C102" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D102">
         <v>36.883333</v>
@@ -5059,27 +5381,30 @@
         <v>35.933332999999998</v>
       </c>
       <c r="J102" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="K102" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="M102" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="O102" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P102" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="103" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="Q102" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="103" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B103" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="C103" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D103">
         <v>31.266667000000002</v>
@@ -5088,27 +5413,30 @@
         <v>32.299999999999997</v>
       </c>
       <c r="J103" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="K103" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="M103" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="O103" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P103" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="104" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="Q103" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="104" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B104" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="C104" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D104">
         <v>44.553930999999999</v>
@@ -5117,27 +5445,30 @@
         <v>12.264552999999999</v>
       </c>
       <c r="J104" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="K104" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="M104" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="O104" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P104" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="105" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+      <c r="Q104" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="105" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B105" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="C105" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D105">
         <v>42.101999999999997</v>
@@ -5146,27 +5477,30 @@
         <v>11.771000000000001</v>
       </c>
       <c r="J105" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="K105" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="M105" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="O105" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P105" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="106" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="Q105" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="106" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B106" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="C106" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D106">
         <v>39.078000000000003</v>
@@ -5175,27 +5509,30 @@
         <v>17.135999999999999</v>
       </c>
       <c r="J106" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="K106" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="M106" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="O106" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P106" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="107" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="Q106" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="107" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B107" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="C107" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D107">
         <v>32.766666999999998</v>
@@ -5204,27 +5541,30 @@
         <v>22.65</v>
       </c>
       <c r="J107" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="K107" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="M107" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="O107" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P107" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="108" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="Q107" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="108" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B108" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C108" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D108">
         <v>36.966500000000003</v>
@@ -5233,27 +5573,30 @@
         <v>-1.9029</v>
       </c>
       <c r="J108" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="K108" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="M108" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="O108" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P108" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="109" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="Q108" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="109" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B109" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="C109" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D109">
         <v>43.416666999999997</v>
@@ -5262,27 +5605,30 @@
         <v>4.8833330000000004</v>
       </c>
       <c r="J109" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="K109" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="M109" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="O109" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P109" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="110" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="Q109" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="110" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B110" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="C110" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D110">
         <v>44.398000000000003</v>
@@ -5291,27 +5637,30 @@
         <v>8.9220000000000006</v>
       </c>
       <c r="J110" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="K110" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="M110" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="O110" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P110" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="111" spans="2:16" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+      <c r="Q110" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="111" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B111" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="C111" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D111">
         <v>39.351709999999997</v>
@@ -5320,27 +5669,30 @@
         <v>22.984500000000001</v>
       </c>
       <c r="J111" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="K111" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="M111" t="s">
-        <v>80</v>
+        <v>82</v>
       </c>
       <c r="O111" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P111" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="112" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="Q111" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="112" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B112" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="C112" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D112">
         <v>36.735732349999999</v>
@@ -5349,27 +5701,30 @@
         <v>36.209483480000003</v>
       </c>
       <c r="J112" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="K112" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="M112" t="s">
-        <v>94</v>
+        <v>96</v>
       </c>
       <c r="O112" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P112" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="113" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="Q112" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="113" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B113" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="C113" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D113">
         <v>38.433332999999998</v>
@@ -5378,27 +5733,30 @@
         <v>27.133333</v>
       </c>
       <c r="J113" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="K113" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="M113" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="O113" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P113" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="114" spans="2:16" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="Q113" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="114" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B114" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="C114" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D114">
         <v>40.933332999999998</v>
@@ -5407,27 +5765,30 @@
         <v>24.4</v>
       </c>
       <c r="J114" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="K114" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="M114" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="O114" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P114" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="115" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="Q114" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="115" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B115" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="C115" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D115">
         <v>32.666666999999997</v>
@@ -5436,27 +5797,30 @@
         <v>14.25</v>
       </c>
       <c r="J115" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="K115" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="M115" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="O115" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P115" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="116" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="Q115" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="116" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B116" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="C116" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D116">
         <v>44.967300000000002</v>
@@ -5465,27 +5829,30 @@
         <v>14.118499999999999</v>
       </c>
       <c r="J116" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="K116" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="M116" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="O116" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P116" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="117" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="Q116" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="117" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B117" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="C117" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D117">
         <v>37.866667</v>
@@ -5494,27 +5861,30 @@
         <v>27.25</v>
       </c>
       <c r="J117" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="K117" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="M117" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="O117" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P117" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="118" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="Q117" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="118" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B118" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="C118" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D118">
         <v>36.716667000000001</v>
@@ -5523,27 +5893,30 @@
         <v>-4.4166670000000003</v>
       </c>
       <c r="J118" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="K118" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="M118" t="s">
-        <v>176</v>
+        <v>178</v>
       </c>
       <c r="O118" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P118" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="119" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="Q118" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="119" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B119" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="C119" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D119">
         <v>36.799999999999997</v>
@@ -5552,27 +5925,30 @@
         <v>34.633333</v>
       </c>
       <c r="J119" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="K119" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="M119" t="s">
-        <v>177</v>
+        <v>179</v>
       </c>
       <c r="O119" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P119" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="120" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="Q119" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="120" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B120" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="C120" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D120">
         <v>45.783332999999999</v>
@@ -5581,27 +5957,30 @@
         <v>13.55</v>
       </c>
       <c r="J120" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="K120" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="M120" t="s">
-        <v>178</v>
+        <v>180</v>
       </c>
       <c r="O120" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P120" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="121" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="Q120" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="121" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B121" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="C121" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D121">
         <v>40.832999999999998</v>
@@ -5610,27 +5989,30 @@
         <v>14.275</v>
       </c>
       <c r="J121" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="K121" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="M121" t="s">
-        <v>179</v>
+        <v>181</v>
       </c>
       <c r="O121" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P121" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="122" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="Q121" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="122" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B122" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="C122" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D122">
         <v>38.766666999999998</v>
@@ -5639,27 +6021,30 @@
         <v>26.916667</v>
       </c>
       <c r="J122" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="K122" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="M122" t="s">
-        <v>180</v>
+        <v>182</v>
       </c>
       <c r="O122" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P122" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="123" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="Q122" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="123" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B123" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="C123" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D123">
         <v>39.566667000000002</v>
@@ -5668,27 +6053,30 @@
         <v>2.6333329999999999</v>
       </c>
       <c r="J123" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="K123" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="M123" t="s">
-        <v>181</v>
+        <v>183</v>
       </c>
       <c r="O123" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P123" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="124" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="Q123" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="124" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B124" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="C124" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D124">
         <v>43.016666999999998</v>
@@ -5697,27 +6085,30 @@
         <v>3.0666669999999998</v>
       </c>
       <c r="J124" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="K124" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="M124" t="s">
-        <v>182</v>
+        <v>184</v>
       </c>
       <c r="O124" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P124" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="125" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="Q124" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="125" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B125" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="C125" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D125">
         <v>41.334000000000003</v>
@@ -5726,27 +6117,30 @@
         <v>16.292000000000002</v>
       </c>
       <c r="J125" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="K125" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="M125" t="s">
-        <v>183</v>
+        <v>185</v>
       </c>
       <c r="O125" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P125" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="126" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="Q125" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="126" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B126" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="C126" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D126">
         <v>45.416666999999997</v>
@@ -5755,27 +6149,30 @@
         <v>12.433332999999999</v>
       </c>
       <c r="J126" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="K126" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="M126" t="s">
-        <v>184</v>
+        <v>186</v>
       </c>
       <c r="O126" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P126" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="127" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+      <c r="Q126" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="127" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B127" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="C127" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D127">
         <v>38.119</v>
@@ -5784,27 +6181,30 @@
         <v>13.38</v>
       </c>
       <c r="J127" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="K127" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="M127" t="s">
-        <v>185</v>
+        <v>187</v>
       </c>
       <c r="O127" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P127" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="128" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="Q127" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="128" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B128" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="C128" t="s">
-        <v>49</v>
+        <v>51</v>
       </c>
       <c r="D128">
         <v>41.383333329999999</v>
@@ -5813,27 +6213,30 @@
         <v>19.416666670000001</v>
       </c>
       <c r="J128" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="K128" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="M128" t="s">
-        <v>186</v>
+        <v>188</v>
       </c>
       <c r="O128" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P128" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="129" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="Q128" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="129" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B129" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="C129" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D129">
         <v>36.716667000000001</v>
@@ -5842,27 +6245,30 @@
         <v>14.85</v>
       </c>
       <c r="J129" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="K129" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="M129" t="s">
-        <v>187</v>
+        <v>189</v>
       </c>
       <c r="O129" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P129" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="130" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="Q129" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="130" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B130" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="C130" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D130">
         <v>39.65</v>
@@ -5871,27 +6277,30 @@
         <v>-0.216667</v>
       </c>
       <c r="J130" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="K130" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="M130" t="s">
-        <v>188</v>
+        <v>190</v>
       </c>
       <c r="O130" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P130" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="131" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="Q130" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="131" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B131" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="C131" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="D131">
         <v>43.733333000000002</v>
@@ -5900,27 +6309,30 @@
         <v>15.883333</v>
       </c>
       <c r="J131" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="K131" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="M131" t="s">
-        <v>189</v>
+        <v>191</v>
       </c>
       <c r="O131" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P131" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="132" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="Q131" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="132" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B132" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="C132" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D132">
         <v>40.466667000000001</v>
@@ -5929,27 +6341,30 @@
         <v>17.2</v>
       </c>
       <c r="J132" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="K132" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="M132" t="s">
-        <v>190</v>
+        <v>192</v>
       </c>
       <c r="O132" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P132" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="133" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="Q132" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="133" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B133" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="C133" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="D133">
         <v>41.1</v>
@@ -5958,24 +6373,27 @@
         <v>1.233333</v>
       </c>
       <c r="J133" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="K133" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="M133" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="O133" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P133" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="134" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="Q133" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="134" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B134" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="D134">
         <v>34.9</v>
@@ -5984,27 +6402,30 @@
         <v>35.866667</v>
       </c>
       <c r="J134" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="K134" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="M134" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="O134" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P134" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="135" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="Q134" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="135" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B135" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="C135" t="s">
-        <v>33</v>
+        <v>35</v>
       </c>
       <c r="D135">
         <v>36.316667000000002</v>
@@ -6013,27 +6434,30 @@
         <v>33.883333</v>
       </c>
       <c r="J135" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="K135" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="M135" t="s">
-        <v>193</v>
+        <v>195</v>
       </c>
       <c r="O135" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P135" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="136" spans="2:16" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="Q135" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="136" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B136" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="C136" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D136">
         <v>40.633333</v>
@@ -6042,27 +6466,30 @@
         <v>22.933333000000001</v>
       </c>
       <c r="J136" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="K136" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="M136" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="O136" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P136" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="137" spans="2:16" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="Q136" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="137" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B137" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="C137" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D137">
         <v>38.335569999999997</v>
@@ -6071,27 +6498,30 @@
         <v>21.84543</v>
       </c>
       <c r="J137" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="K137" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="M137" t="s">
-        <v>118</v>
+        <v>120</v>
       </c>
       <c r="O137" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P137" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="138" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="Q137" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="138" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B138" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="C138" t="s">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D138">
         <v>43.1</v>
@@ -6100,27 +6530,30 @@
         <v>5.9166670000000003</v>
       </c>
       <c r="J138" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="K138" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="M138" t="s">
-        <v>195</v>
+        <v>197</v>
       </c>
       <c r="O138" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P138" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="139" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="Q138" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="139" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B139" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="C139" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="D139">
         <v>45.611255</v>
@@ -6129,27 +6562,30 @@
         <v>13.802586</v>
       </c>
       <c r="J139" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="K139" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="M139" t="s">
-        <v>196</v>
+        <v>198</v>
       </c>
       <c r="O139" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P139" t="s">
-        <v>21</v>
-      </c>
-    </row>
-    <row r="140" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>23</v>
+      </c>
+      <c r="Q139" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="140" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B140" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="C140" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="D140">
         <v>34.721699999999998</v>
@@ -6158,27 +6594,30 @@
         <v>33.316400000000002</v>
       </c>
       <c r="J140" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="K140" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="M140" t="s">
-        <v>128</v>
+        <v>130</v>
       </c>
       <c r="O140" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P140" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="141" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="Q140" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="141" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B141" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="C141" t="s">
-        <v>38</v>
+        <v>40</v>
       </c>
       <c r="D141">
         <v>31.349048100000001</v>
@@ -6187,27 +6626,30 @@
         <v>30.318646600000001</v>
       </c>
       <c r="J141" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="K141" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="M141" t="s">
-        <v>197</v>
+        <v>199</v>
       </c>
       <c r="O141" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P141" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="142" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="Q141" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="142" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B142" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="C142" t="s">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="D142">
         <v>32.336415289999998</v>
@@ -6216,27 +6658,30 @@
         <v>15.219913979999999</v>
       </c>
       <c r="J142" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="K142" t="s">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="M142" t="s">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="O142" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P142" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="143" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="Q142" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="143" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B143" t="s">
-        <v>35</v>
+        <v>37</v>
       </c>
       <c r="C143" t="s">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D143">
         <v>34.33510777</v>
@@ -6245,27 +6690,30 @@
         <v>35.731147280000002</v>
       </c>
       <c r="J143" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="K143" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="M143" t="s">
+        <v>37</v>
+      </c>
+      <c r="O143" t="s">
+        <v>23</v>
+      </c>
+      <c r="P143" t="s">
+        <v>24</v>
+      </c>
+      <c r="Q143" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="144" spans="2:17" x14ac:dyDescent="0.35">
+      <c r="B144" t="s">
+        <v>200</v>
+      </c>
+      <c r="C144" t="s">
         <v>35</v>
-      </c>
-      <c r="O143" t="s">
-        <v>21</v>
-      </c>
-      <c r="P143" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="144" spans="2:16" hidden="1" x14ac:dyDescent="0.35">
-      <c r="B144" t="s">
-        <v>198</v>
-      </c>
-      <c r="C144" t="s">
-        <v>33</v>
       </c>
       <c r="D144">
         <v>39.879589000000003</v>
@@ -6274,27 +6722,30 @@
         <v>26.156554</v>
       </c>
       <c r="J144" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="K144" t="s">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="M144" t="s">
-        <v>198</v>
+        <v>200</v>
       </c>
       <c r="O144" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P144" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="145" spans="2:16" x14ac:dyDescent="0.35">
+        <v>24</v>
+      </c>
+      <c r="Q144" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="145" spans="2:17" x14ac:dyDescent="0.35">
       <c r="B145" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="C145" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="D145">
         <v>37.96</v>
@@ -6303,29 +6754,25 @@
         <v>23.4023</v>
       </c>
       <c r="J145" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="K145" t="s">
-        <v>156</v>
+        <v>158</v>
       </c>
       <c r="M145" t="s">
-        <v>199</v>
+        <v>201</v>
       </c>
       <c r="O145" t="s">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="P145" t="s">
-        <v>22</v>
+        <v>24</v>
+      </c>
+      <c r="Q145" t="s">
+        <v>24</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:P145" xr:uid="{00000000-0001-0000-0000-000000000000}">
-    <filterColumn colId="2">
-      <filters>
-        <filter val="GR"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>